--- a/uploads/Template_Produtos_Mpozenato_Cadastro_VILARICA.xlsx
+++ b/uploads/Template_Produtos_Mpozenato_Cadastro_VILARICA.xlsx
@@ -3437,7 +3437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT16"/>
+  <dimension ref="A1:AT11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="50.28515625" defaultRowHeight="22.5" customHeight="1"/>
   <cols>
     <col width="25.85546875" customWidth="1" style="3" min="1" max="1"/>
@@ -3950,12 +3950,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7901064702707</t>
+          <t>7901064725362</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10045-91</t>
+          <t>20037-107</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3963,22 +3963,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MULTIUSO LINE/ALINE IMBUIA/CHP</t>
+          <t>COMODA DUBAI INT/DELMONT NATURE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MULTIUSO LINE/ALINE IMBUI</t>
+          <t xml:space="preserve">COMODA DUBAI INT/DELMONT </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MULTIUSO LINE/ALINE IMBUIA/CHP</t>
+          <t>COMODA DUBAI INT/DELMONT NATURE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MULTIUSO LINE/ALINE IMBUIA/CHP</t>
+          <t>COMODA DUBAI INT/DELMONT NATURE</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -3988,16 +3988,18 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>COZINHA</t>
+          <t>COMODA</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ARMÁRIOS MULTI-USO</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>73</v>
+          <t>CÔMODAS</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Cômoda Quarto 121cm 8 Gavetas Delmont Nature V02 - Mpozenato COD FAB: 20037-107 COR: NATURE</t>
+        </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -4015,22 +4017,32 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>37</v>
-      </c>
-      <c r="W3" t="n">
-        <v>36</v>
-      </c>
-      <c r="X3" t="n">
-        <v>61</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>190</v>
+        <v>2</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="AB3" t="n">
         <v>90</v>
@@ -4038,8 +4050,10 @@
       <c r="AC3" t="n">
         <v>1000</v>
       </c>
-      <c r="AD3" t="n">
-        <v>3</v>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -4083,7 +4097,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>Armário Multiuso 60cm Com 2 Portas Aline Imbuia/Champanhe V02 - Mpozenato</t>
+          <t>Cômoda Quarto 121cm 8 Gavetas Delmont Nature V02 - Mpozenato</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -4096,15 +4110,46 @@
           <t>90 dias após o recebimento do produto</t>
         </is>
       </c>
-      <c r="AQ3" t="n">
-        <v>3</v>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>&lt;B&gt;Armário Multiuso 60cm Com 2 Portas Aline Imbuia/Champanhe V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;Básico e versátil, este &lt;b&gt;Armário Multiuso&lt;/b&gt; é ideal para manter cada espaço da casa sempre bem organizado e funcional. &lt;br&gt;&lt;br&gt;
-Com design tradicional, possui duas portas e cinco prateleiras internas que acomodam desde utensílios da &lt;b&gt;Cozinha&lt;/b&gt; até roupas e acessórios. &lt;br&gt;&lt;br&gt;
-A versatilidade permite o uso também na &lt;b&gt;Lavanderia&lt;/b&gt;, &lt;b&gt;Quarto&lt;/b&gt; ou &lt;b&gt;Home Office&lt;/b&gt;, ajudando a manter tudo no seu devido lugar de forma prática. &lt;br&gt;&lt;br&gt;
-Fabricado com materiais resistentes, garante durabilidade e eficiência no dia a dia, atendendo diferentes necessidades de armazenamento. &lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;ESPECIFICAÇÕES&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;&lt;BR&gt;Então, adicione esse &lt;B&gt;armário multiuso&lt;/B&gt; ao seu carrinho e leve receba funcionalidade e bem-estar! &lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;Dimensões dos Produtos&lt;/B&gt;&lt;BR&gt;&lt;B&gt;Largura: &lt;/B&gt;60 cm. &lt;BR&gt;&lt;B&gt;Altura: &lt;/B&gt;190 cm. &lt;BR&gt;&lt;B&gt;Profundidade: &lt;/B&gt;40 cm. &lt;BR&gt;&lt;B&gt;Peso: &lt;/B&gt;36 kg. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Características do Produto&lt;/B&gt;&lt;BR&gt;&lt;B&gt;Material da estrutura: &lt;/B&gt;MDP 12mm/15mm. &lt;BR&gt;&lt;B&gt;Acabamento: &lt;/B&gt;Pintura UV. &lt;BR&gt;&lt;B&gt;Escala de Brilho: &lt;/B&gt;Fosco. &lt;BR&gt;&lt;B&gt;Peso Suportado: &lt;/B&gt;5 kg por prateleira. &lt;BR&gt;&lt;B&gt;Quantidade de Portas: &lt;/B&gt;2 Portas. &lt;BR&gt;&lt;B&gt;Material dos Puxadores: &lt;/B&gt;Plástico. &lt;BR&gt;&lt;B&gt;Quantidade de Prateleiras: &lt;/B&gt;5 Prateleiras. &lt;BR&gt;&lt;B&gt;Quantidade de Nichos: &lt;/B&gt;6 Nichos. &lt;BR&gt;&lt;B&gt;Possui Pés: &lt;/B&gt;Sim. &lt;BR&gt;&lt;B&gt;Tipo de Pés: &lt;/B&gt;Madeira/Sapatas Plásticas. &lt;BR&gt;&lt;B&gt;Diferenciais: &lt;/B&gt;&lt;BR&gt;- Design clássico. &lt;BR&gt;- Fundo em MDF 3mm. &lt;BR&gt;- Prateleiras superiores móveis com regulagem de altura. &lt;BR&gt;- Pode-se optar pela instalação dos pés ou das sapatas. &lt;BR&gt;- Armário multiuso com 6 repartições internas. &lt;BR&gt;&lt;B&gt;Sistema de Montagem: &lt;/B&gt;Parafusos/Cavilhas/Cantoneira. &lt;BR&gt;&lt;B&gt;Manual de Montagem: &lt;/B&gt;Sim. &lt;BR&gt;&lt;B&gt;Complexidade da Montagem: &lt;/B&gt;Média. &lt;BR&gt;&lt;B&gt;Volumes: &lt;/B&gt;1 Volume. &lt;BR&gt;&lt;B&gt;Conteúdo da Embalagem: &lt;/B&gt;1 Armário Multiuso. &lt;BR&gt;&lt;B&gt;Garantia do Fabricante: &lt;/B&gt;90 dias contra defeito de fabricação. &lt;BR&gt;&lt;B&gt;Montagem: &lt;/B&gt;Recomendamos que seja feita por um profissional. &lt;BR&gt;&lt;B&gt;Recomendação de Limpeza: &lt;/B&gt;Utilize pano levemente úmido. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Observações importantes&lt;/B&gt;&lt;BR&gt;- Produto para uso residencial em ambiente interno, não devendo ficar exposto diretamente ao sol, calor e umidades excessivas. &lt;BR&gt;- Pode haver alguma diferença de tonalidade entre a imagem e o produto real, por conta do tratamento de imagens e a calibração de cores do seu monitor. &lt;BR&gt;- As imagens são meramente ilustrativas, não acompanham objetos de decoração e eletrônicos. &lt;BR&gt;- Confira o estado da embalagem, não devendo assinar o comprovante em caso de danos. &lt;BR&gt;- Não asseguramos, no ato da entrega, por subir escadas/elevadores, pelo transporte por guincho em apartamentos ou montagem, desmontagem e instalações. Eventuais despesas são por conta do comprador. &lt;BR&gt;- Confira as dimensões do produto e certifique-se de que passará normalmente por supostos elevadores, portas, escadas e/ou corredores de sua residência. &lt;BR&gt;</t>
+          <t xml:space="preserve">&lt;B&gt;Cômoda Quarto 121cm 8 Gavetas Delmont Nature V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt; Desenvolvida para ir além do convencional, entrega sofisticação, estilo e presença marcante, elevando a composição do &lt;b&gt;Quarto&lt;/b&gt; com elegância. A &lt;b&gt;Cômoda&lt;/b&gt; moderna e acabamento refinado, ideal para ambientes bem planejados.&lt;br&gt;&lt;br&gt;
+O tampo em MDP de 25mm oferece superfície ampla e resistente para acomodar objetos decorativos ou itens de uso diário. A estrutura em MDF proporciona estabilidade, segurança e excelente durabilidade.&lt;br&gt;&lt;br&gt;
+&lt;b&gt;Cômoda 8 Gavetas&lt;/b&gt;, que garante ótima capacidade de organização no dia a dia. Duas delas são gavetões profundos com fundo reforçado, ideais para peças volumosas e itens maiores.&lt;br&gt;&lt;br&gt;
+As gavetas da &lt;b&gt;Cômoda&lt;/b&gt; possuem corrediças telescópicas, assegurando abertura suave e maior vida útil ao móvel. Já os puxadores em alumínio acrescentam um toque atual e sofisticado, unindo resistência e beleza em cada detalhe. &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;ESPECIFICAÇÕES&lt;/b&gt; &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;Dimensões do Produto&lt;/b&gt;&lt;br /&gt;                
+&lt;b&gt;Largura:&lt;/b&gt;        121 cm.        &lt;br /&gt;
+&lt;b&gt;Altura:&lt;/b&gt;        104 cm.        &lt;br /&gt;
+&lt;b&gt;Profundidade:&lt;/b&gt;        47 cm.        &lt;br /&gt;
+&lt;b&gt;Peso:&lt;/b&gt;        63 Kg.        &lt;br /&gt;
+&lt;br /&gt;                
+&lt;b&gt;Características do Produto&lt;/b&gt;&lt;br /&gt;                
+&lt;b&gt;Material da Estrutura:&lt;/b&gt;        MDF/MDP.        &lt;br /&gt;
+&lt;b&gt;Espessura das Chapas:&lt;/b&gt;        12mm/15mm/25mm.        &lt;br /&gt;
+&lt;b&gt;Peso Suportado:&lt;/b&gt;        28 kg Distribuídos.        &lt;br /&gt;
+&lt;b&gt;Acabamento:&lt;/b&gt;        Pintura UV.        &lt;br /&gt;
+&lt;b&gt;Escala de Brilho:&lt;/b&gt;        Fosco.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Gavetas:&lt;/b&gt;        8 gavetas.        &lt;br /&gt;
+&lt;b&gt;Tipo de Corrediças:&lt;/b&gt;        Telescópicas.        &lt;br /&gt;
+&lt;b&gt;Tipo de Puxador:&lt;/b&gt;        Alumínio.        &lt;br /&gt;
+&lt;b&gt;Diferenciais:&lt;/b&gt;&lt;br /&gt;                
+- Design moderno.&lt;br /&gt;                
+- 2 gavetões.&lt;br&gt;                
+- Tampo de 25mm MDP.&lt;br /&gt;                
+- Corrediças telescópicas.&lt;br /&gt;                
+- Puxador em alumínio.&lt;br&gt;                
+&lt;b&gt;Sistema de Montagem:&lt;/b&gt;        Cavilhas / Parafusos.        &lt;br /&gt;
+&lt;b&gt;Manual de Montagem:&lt;/b&gt;        Sim.        &lt;br /&gt;
+&lt;b&gt;Complexidade da Montagem:&lt;/b&gt;        Média.        &lt;br /&gt;
+&lt;b&gt;Volumes:&lt;/b&gt;        2 Volumes.        &lt;br /&gt;
+&lt;b&gt;Conteúdo da embalagem:&lt;/b&gt;        1 Cômoda.        &lt;br /&gt;
+&lt;b&gt;Garantia do Fabricante:&lt;/b&gt;        90 dias contra defeito de fabricação.        &lt;br /&gt;
+&lt;b&gt;Montagem:&lt;/b&gt;         Recomendamos que seja feita por um profissional.        &lt;br /&gt;
+&lt;b&gt;Recomendação de Limpeza:&lt;/b&gt;         Pano levemente úmido e detergente neutro.        &lt;br /&gt;
+</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -4121,12 +4166,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7901064702714</t>
+          <t>7901064725379</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10045-80</t>
+          <t>20037-111</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4134,22 +4179,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MULTIUSO LINE/ALINE IMBUIA</t>
+          <t>COMODA DUBAI INT/DELMONT NATURE/ALASCA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MULTIUSO LINE/ALINE IMBUI</t>
+          <t xml:space="preserve">COMODA DUBAI INT/DELMONT </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MULTIUSO LINE/ALINE IMBUIA</t>
+          <t>COMODA DUBAI INT/DELMONT NATURE/ALASCA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MULTIUSO LINE/ALINE IMBUIA</t>
+          <t>COMODA DUBAI INT/DELMONT NATURE/ALASCA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -4159,16 +4204,18 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>COZINHA</t>
+          <t>COMODA</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ARMÁRIOS MULTI-USO</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>63</v>
+          <t>CÔMODAS</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Cômoda Quarto 121cm 8 Gavetas Delmont Nature/Alasca V02 - Mpozenato COD FAB: 20037-111 COR: NATURE/ALASCA</t>
+        </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -4186,22 +4233,32 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>37</v>
-      </c>
-      <c r="W4" t="n">
-        <v>36</v>
-      </c>
-      <c r="X4" t="n">
-        <v>61</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>190</v>
+        <v>2</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="AB4" t="n">
         <v>90</v>
@@ -4209,8 +4266,10 @@
       <c r="AC4" t="n">
         <v>1000</v>
       </c>
-      <c r="AD4" t="n">
-        <v>3</v>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -4254,7 +4313,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>Armário Multiuso 60cm Com 2 Portas Aline Imbuia V02 - Mpozenato</t>
+          <t>Cômoda Quarto 121cm 8 Gavetas Delmont Nature/Alasca V02 - Mpozenato</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -4267,15 +4326,46 @@
           <t>90 dias após o recebimento do produto</t>
         </is>
       </c>
-      <c r="AQ4" t="n">
-        <v>3</v>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>&lt;B&gt;Armário Multiuso 60cm Com 2 Portas Aline Imbuia V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;Básico e versátil, este &lt;b&gt;Armário Multiuso&lt;/b&gt; é ideal para manter cada espaço da casa sempre bem organizado e funcional. &lt;br&gt;&lt;br&gt;
-Com design tradicional, possui duas portas e cinco prateleiras internas que acomodam desde utensílios da &lt;b&gt;Cozinha&lt;/b&gt; até roupas e acessórios. &lt;br&gt;&lt;br&gt;
-A versatilidade permite o uso também na &lt;b&gt;Lavanderia&lt;/b&gt;, &lt;b&gt;Quarto&lt;/b&gt; ou &lt;b&gt;Home Office&lt;/b&gt;, ajudando a manter tudo no seu devido lugar de forma prática. &lt;br&gt;&lt;br&gt;
-Fabricado com materiais resistentes, garante durabilidade e eficiência no dia a dia, atendendo diferentes necessidades de armazenamento. &lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;ESPECIFICAÇÕES&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;&lt;BR&gt;Então, adicione esse &lt;B&gt;armário multiuso&lt;/B&gt; ao seu carrinho e leve receba funcionalidade e bem-estar! &lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;Dimensões dos Produtos&lt;/B&gt;&lt;BR&gt;&lt;B&gt;Largura: &lt;/B&gt;60 cm. &lt;BR&gt;&lt;B&gt;Altura: &lt;/B&gt;190 cm. &lt;BR&gt;&lt;B&gt;Profundidade: &lt;/B&gt;40 cm. &lt;BR&gt;&lt;B&gt;Peso: &lt;/B&gt;36 kg. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Características do Produto&lt;/B&gt;&lt;BR&gt;&lt;B&gt;Material da estrutura: &lt;/B&gt;MDP 12mm/15mm. &lt;BR&gt;&lt;B&gt;Acabamento: &lt;/B&gt;Pintura UV. &lt;BR&gt;&lt;B&gt;Escala de Brilho: &lt;/B&gt;Fosco. &lt;BR&gt;&lt;B&gt;Peso Suportado: &lt;/B&gt;5 kg por prateleira. &lt;BR&gt;&lt;B&gt;Quantidade de Portas: &lt;/B&gt;2 Portas. &lt;BR&gt;&lt;B&gt;Material dos Puxadores: &lt;/B&gt;Plástico. &lt;BR&gt;&lt;B&gt;Quantidade de Prateleiras: &lt;/B&gt;5 Prateleiras. &lt;BR&gt;&lt;B&gt;Quantidade de Nichos: &lt;/B&gt;6 Nichos. &lt;BR&gt;&lt;B&gt;Possui Pés: &lt;/B&gt;Sim. &lt;BR&gt;&lt;B&gt;Tipo de Pés: &lt;/B&gt;Madeira/Sapatas Plásticas. &lt;BR&gt;&lt;B&gt;Diferenciais: &lt;/B&gt;&lt;BR&gt;- Design clássico. &lt;BR&gt;- Fundo em MDF 3mm. &lt;BR&gt;- Prateleiras superiores móveis com regulagem de altura. &lt;BR&gt;- Pode-se optar pela instalação dos pés ou das sapatas. &lt;BR&gt;- Armário multiuso com 6 repartições internas. &lt;BR&gt;&lt;B&gt;Sistema de Montagem: &lt;/B&gt;Parafusos/Cavilhas/Cantoneira. &lt;BR&gt;&lt;B&gt;Manual de Montagem: &lt;/B&gt;Sim. &lt;BR&gt;&lt;B&gt;Complexidade da Montagem: &lt;/B&gt;Média. &lt;BR&gt;&lt;B&gt;Volumes: &lt;/B&gt;1 Volume. &lt;BR&gt;&lt;B&gt;Conteúdo da Embalagem: &lt;/B&gt;1 Armário Multiuso. &lt;BR&gt;&lt;B&gt;Garantia do Fabricante: &lt;/B&gt;90 dias contra defeito de fabricação. &lt;BR&gt;&lt;B&gt;Montagem: &lt;/B&gt;Recomendamos que seja feita por um profissional. &lt;BR&gt;&lt;B&gt;Recomendação de Limpeza: &lt;/B&gt;Utilize pano levemente úmido. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Observações importantes&lt;/B&gt;&lt;BR&gt;- Produto para uso residencial em ambiente interno, não devendo ficar exposto diretamente ao sol, calor e umidades excessivas. &lt;BR&gt;- Pode haver alguma diferença de tonalidade entre a imagem e o produto real, por conta do tratamento de imagens e a calibração de cores do seu monitor. &lt;BR&gt;- As imagens são meramente ilustrativas, não acompanham objetos de decoração e eletrônicos. &lt;BR&gt;- Confira o estado da embalagem, não devendo assinar o comprovante em caso de danos. &lt;BR&gt;- Não asseguramos, no ato da entrega, por subir escadas/elevadores, pelo transporte por guincho em apartamentos ou montagem, desmontagem e instalações. Eventuais despesas são por conta do comprador. &lt;BR&gt;- Confira as dimensões do produto e certifique-se de que passará normalmente por supostos elevadores, portas, escadas e/ou corredores de sua residência. &lt;BR&gt;</t>
+          <t xml:space="preserve">&lt;B&gt;Cômoda Quarto 121cm 8 Gavetas Delmont Nature/Alasca V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt; Desenvolvida para ir além do convencional, entrega sofisticação, estilo e presença marcante, elevando a composição do &lt;b&gt;Quarto&lt;/b&gt; com elegância. A &lt;b&gt;Cômoda&lt;/b&gt; moderna e acabamento refinado, ideal para ambientes bem planejados.&lt;br&gt;&lt;br&gt;
+O tampo em MDP de 25mm oferece superfície ampla e resistente para acomodar objetos decorativos ou itens de uso diário. A estrutura em MDF proporciona estabilidade, segurança e excelente durabilidade.&lt;br&gt;&lt;br&gt;
+&lt;b&gt;Cômoda 8 Gavetas&lt;/b&gt;, que garante ótima capacidade de organização no dia a dia. Duas delas são gavetões profundos com fundo reforçado, ideais para peças volumosas e itens maiores.&lt;br&gt;&lt;br&gt;
+As gavetas da &lt;b&gt;Cômoda&lt;/b&gt; possuem corrediças telescópicas, assegurando abertura suave e maior vida útil ao móvel. Já os puxadores em alumínio acrescentam um toque atual e sofisticado, unindo resistência e beleza em cada detalhe. &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;ESPECIFICAÇÕES&lt;/b&gt; &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;Dimensões do Produto&lt;/b&gt;&lt;br /&gt;                
+&lt;b&gt;Largura:&lt;/b&gt;        121 cm.        &lt;br /&gt;
+&lt;b&gt;Altura:&lt;/b&gt;        104 cm.        &lt;br /&gt;
+&lt;b&gt;Profundidade:&lt;/b&gt;        47 cm.        &lt;br /&gt;
+&lt;b&gt;Peso:&lt;/b&gt;        63 Kg.        &lt;br /&gt;
+&lt;br /&gt;                
+&lt;b&gt;Características do Produto&lt;/b&gt;&lt;br /&gt;                
+&lt;b&gt;Material da Estrutura:&lt;/b&gt;        MDF/MDP.        &lt;br /&gt;
+&lt;b&gt;Espessura das Chapas:&lt;/b&gt;        12mm/15mm/25mm.        &lt;br /&gt;
+&lt;b&gt;Peso Suportado:&lt;/b&gt;        28 kg Distribuídos.        &lt;br /&gt;
+&lt;b&gt;Acabamento:&lt;/b&gt;        Pintura UV.        &lt;br /&gt;
+&lt;b&gt;Escala de Brilho:&lt;/b&gt;        Fosco.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Gavetas:&lt;/b&gt;        8 gavetas.        &lt;br /&gt;
+&lt;b&gt;Tipo de Corrediças:&lt;/b&gt;        Telescópicas.        &lt;br /&gt;
+&lt;b&gt;Tipo de Puxador:&lt;/b&gt;        Alumínio.        &lt;br /&gt;
+&lt;b&gt;Diferenciais:&lt;/b&gt;&lt;br /&gt;                
+- Design moderno.&lt;br /&gt;                
+- 2 gavetões.&lt;br&gt;                
+- Tampo de 25mm MDP.&lt;br /&gt;                
+- Corrediças telescópicas.&lt;br /&gt;                
+- Puxador em alumínio.&lt;br&gt;                
+&lt;b&gt;Sistema de Montagem:&lt;/b&gt;        Cavilhas / Parafusos.        &lt;br /&gt;
+&lt;b&gt;Manual de Montagem:&lt;/b&gt;        Sim.        &lt;br /&gt;
+&lt;b&gt;Complexidade da Montagem:&lt;/b&gt;        Média.        &lt;br /&gt;
+&lt;b&gt;Volumes:&lt;/b&gt;        2 Volumes.        &lt;br /&gt;
+&lt;b&gt;Conteúdo da embalagem:&lt;/b&gt;        1 Cômoda.        &lt;br /&gt;
+&lt;b&gt;Garantia do Fabricante:&lt;/b&gt;        90 dias contra defeito de fabricação.        &lt;br /&gt;
+&lt;b&gt;Montagem:&lt;/b&gt;         Recomendamos que seja feita por um profissional.        &lt;br /&gt;
+&lt;b&gt;Recomendação de Limpeza:&lt;/b&gt;         Pano levemente úmido e detergente neutro.        &lt;br /&gt;
+</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -4292,12 +4382,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7901064702721</t>
+          <t>7901064725386</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10090-127</t>
+          <t>20037-113</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4305,22 +4395,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GR 4 PT IDEAL/MAYRA NT/CHP/BRISA</t>
+          <t>COMODA DUBAI INT/DELMONT NATURE/CAMARIM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GR 4 PT IDEAL/MAYRA NT/CH</t>
+          <t xml:space="preserve">COMODA DUBAI INT/DELMONT </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GR 4 PT IDEAL/MAYRA NT/CHP/BRISA</t>
+          <t>COMODA DUBAI INT/DELMONT NATURE/CAMARIM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>GR 4 PT IDEAL/MAYRA NT/CHP/BRISA</t>
+          <t>COMODA DUBAI INT/DELMONT NATURE/CAMARIM</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -4330,16 +4420,18 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>GUARDA ROUPAS</t>
+          <t>COMODA</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>GUARDA ROUPAS</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>79</v>
+          <t>CÔMODAS</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Cômoda Quarto 121cm 8 Gavetas Delmont Nature/Camarim V02 - Mpozenato COD FAB: 20037-113 COR: NATURE/CAMARIM</t>
+        </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -4357,22 +4449,32 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>44</v>
-      </c>
-      <c r="W5" t="n">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
-        <v>51</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>180</v>
+        <v>2</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="AB5" t="n">
         <v>90</v>
@@ -4380,8 +4482,10 @@
       <c r="AC5" t="n">
         <v>1000</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3</v>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -4425,7 +4529,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>Guarda Roupa Solteiro 103cm Com 4 Portas Mayra Nature/Champanhe V02 - Mpozenato</t>
+          <t>Cômoda Quarto 121cm 8 Gavetas Delmont Nature/Camarim V02 - Mpozenato</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -4438,12 +4542,46 @@
           <t>90 dias após o recebimento do produto</t>
         </is>
       </c>
-      <c r="AQ5" t="n">
-        <v>3</v>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>&lt;B&gt;Guarda Roupa Solteiro 103cm Com 4 Portas Mayra Nature/Champanhe V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;O &lt;B&gt;Guarda Roupa Mayra&lt;/B&gt; é a solução compacta e funcional para quem busca otimizar o espaço sem abrir mão da organização. Com quatro portas e duas gavetas, ele oferece espaço interno para acomodar suas roupas, sapatos e outros pertences. Suas cincos prateleiras são perfeitas para manter tudo organizado, enquanto o espaço para cabides facilita o acesso rápido às suas peças favoritas. &lt;BR&gt;&lt;BR&gt;Este &lt;B&gt;Guarda Roupa&lt;/B&gt; foi projetado para oferecer praticidade no dia a dia. As gavetas são equipadas com corrediças metálicas, garantindo durabilidade e facilidade de uso, enquanto os puxadores oferecem uma pegada confortável e ergonômica. &lt;BR&gt;&lt;BR&gt;Os pés elevados do guarda roupa protegem o móvel da umidade, aumentando sua vida útil e garantindo uma melhor circulação de ar. Além disso, o design do guarda roupa é pensado para valorizar o ambiente e trazer uma sensação de aconchego e sofisticação ao seu quarto. &lt;BR&gt;&lt;BR&gt;Compacto e altamente funcional, é a escolha perfeita para quem busca praticidade, durabilidade e estilo. Seu design inteligente e detalhado proporciona uma excelente experiência no seu &lt;B&gt;Quarto Solteiro&lt;/B&gt;, mantendo tudo organizado e ao seu alcance com muito mais facilidade. &lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;ESPECIFICAÇÕES&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;Dimensões do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Largura&lt;/B&gt;: 103 cm. &lt;BR&gt;&lt;B&gt;Altura:&lt;/B&gt; 181 cm. &lt;BR&gt;&lt;B&gt;Profundidade:&lt;/B&gt; 40 cm. &lt;BR&gt;&lt;B&gt;Peso:&lt;/B&gt; 43,5 Kg. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Características do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Material da Estrutura:&lt;/B&gt; MDP. &lt;BR&gt;&lt;B&gt;Espessura das Chapas:&lt;/B&gt; 12mm &lt;BR&gt;&lt;B&gt;Material do Fundo:&lt;/B&gt; MDF 3mm. &lt;BR&gt;&lt;B&gt;Peso Suportado:&lt;/B&gt; 31 kg distribuídos. &lt;BR&gt;&lt;B&gt;Acabamento:&lt;/B&gt; Pintura UV. &lt;BR&gt;&lt;B&gt;Escala de Brilho:&lt;/B&gt; Acetinado/Fosco. &lt;BR&gt;&lt;B&gt;Quantidade de Portas:&lt;/B&gt; 4 Portas. &lt;BR&gt;&lt;B&gt;Material da Dobradiça:&lt;/B&gt; Metal. &lt;BR&gt;&lt;B&gt;Tipo de Porta:&lt;/B&gt; Convencional. &lt;BR&gt;&lt;B&gt;Possui Cabideiros:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Cabideiro:&lt;/B&gt; 1 Cabideiro. &lt;BR&gt;&lt;B&gt;Material do Cabideiro:&lt;/B&gt; Madeira. &lt;BR&gt;&lt;B&gt;Possui Gaveta:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Gavetas:&lt;/B&gt; 2 Gavetas. &lt;BR&gt;&lt;B&gt;Tipo de Corrediças:&lt;/B&gt; Metálicas. &lt;BR&gt;&lt;B&gt;Material do Puxador:&lt;/B&gt; Plástico ABS. &lt;BR&gt;&lt;B&gt;Possui Prateleiras:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Prateleiras:&lt;/B&gt; 5 Prateleiras. &lt;BR&gt;&lt;B&gt;Possui Pés:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Pés:&lt;/B&gt; 4 Pés. &lt;BR&gt;&lt;B&gt;Material dos Pés: &lt;/B&gt;Plástico PVC. &lt;BR&gt;&lt;B&gt;Possui Espelho:&lt;/B&gt; Não. &lt;BR&gt;&lt;B&gt;Diferenciais: &lt;/B&gt;&lt;BR&gt;- Prateleiras amplas.&lt;BR&gt;- Corrediças metálicas.&lt;BR&gt;- Desing moderno.&lt;BR&gt;- Portas com dobradiça Metálicas.&lt;BR&gt;&lt;B&gt;Sistema de Montagem:&lt;/B&gt; Cavilhas/Parafusos. &lt;BR&gt;&lt;B&gt;Manual de Montagem:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Complexidade da Montagem:&lt;/B&gt; Média. &lt;BR&gt;&lt;B&gt;Volumes:&lt;/B&gt; 1 Volume. &lt;BR&gt;&lt;B&gt;Conteúdo da embalagem:&lt;/B&gt; 1 Guarda Roupa. &lt;BR&gt;&lt;B&gt;Garantia do Fabricante:&lt;/B&gt; 90 dias contra defeito de fabricação. &lt;BR&gt;&lt;B&gt;Montagem:&lt;/B&gt; Recomendamos que seja feita por um profissional. &lt;BR&gt;&lt;B&gt;Recomendação de Limpeza:&lt;/B&gt; Utilize pano levemente úmido. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Observações importantes &lt;/B&gt;&lt;BR&gt;- Produto para uso residencial em ambiente interno, não devendo ficar exposto diretamente ao sol, calor e umidades excessivas.&lt;BR&gt;- Pode haver alguma diferença de tonalidade entre a imagem e o produto real, por conta do tratamento de imagens e a calibração de cores do seu monitor.&lt;BR&gt;- As imagens são meramente ilustrativas, não acompanham objetos de decoração e eletrônicos.&lt;BR&gt;- Ao receber a mercadoria, o cliente deve verificar as condições da embalagem, caso haja algum problema não assine o comprovante de recebimento.&lt;BR&gt;- Montagem, desmontagem e outras instalações serão de responsabilidade do cliente. Não nos responsabilizamos, no ato da entrega, por subir escadas/elevadores ou pelo transporte por guincho em apartamentos. Eventuais despesas são de responsabilidade do comprador.&lt;BR&gt;- Confira as dimensões do produto e certifique-se de que passará normalmente por supostos elevadores, portas, escadas e/ou corredores de sua residência.</t>
+          <t xml:space="preserve">&lt;B&gt;Cômoda Quarto 121cm 8 Gavetas Delmont Nature/Camarim V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt; Desenvolvida para ir além do convencional, entrega sofisticação, estilo e presença marcante, elevando a composição do &lt;b&gt;Quarto&lt;/b&gt; com elegância. A &lt;b&gt;Cômoda&lt;/b&gt; moderna e acabamento refinado, ideal para ambientes bem planejados.&lt;br&gt;&lt;br&gt;
+O tampo em MDP de 25mm oferece superfície ampla e resistente para acomodar objetos decorativos ou itens de uso diário. A estrutura em MDF proporciona estabilidade, segurança e excelente durabilidade.&lt;br&gt;&lt;br&gt;
+&lt;b&gt;Cômoda 8 Gavetas&lt;/b&gt;, que garante ótima capacidade de organização no dia a dia. Duas delas são gavetões profundos com fundo reforçado, ideais para peças volumosas e itens maiores.&lt;br&gt;&lt;br&gt;
+As gavetas da &lt;b&gt;Cômoda&lt;/b&gt; possuem corrediças telescópicas, assegurando abertura suave e maior vida útil ao móvel. Já os puxadores em alumínio acrescentam um toque atual e sofisticado, unindo resistência e beleza em cada detalhe. &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;ESPECIFICAÇÕES&lt;/b&gt; &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;Dimensões do Produto&lt;/b&gt;&lt;br /&gt;                
+&lt;b&gt;Largura:&lt;/b&gt;        121 cm.        &lt;br /&gt;
+&lt;b&gt;Altura:&lt;/b&gt;        104 cm.        &lt;br /&gt;
+&lt;b&gt;Profundidade:&lt;/b&gt;        47 cm.        &lt;br /&gt;
+&lt;b&gt;Peso:&lt;/b&gt;        63 Kg.        &lt;br /&gt;
+&lt;br /&gt;                
+&lt;b&gt;Características do Produto&lt;/b&gt;&lt;br /&gt;                
+&lt;b&gt;Material da Estrutura:&lt;/b&gt;        MDF/MDP.        &lt;br /&gt;
+&lt;b&gt;Espessura das Chapas:&lt;/b&gt;        12mm/15mm/25mm.        &lt;br /&gt;
+&lt;b&gt;Peso Suportado:&lt;/b&gt;        28 kg Distribuídos.        &lt;br /&gt;
+&lt;b&gt;Acabamento:&lt;/b&gt;        Pintura UV.        &lt;br /&gt;
+&lt;b&gt;Escala de Brilho:&lt;/b&gt;        Fosco.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Gavetas:&lt;/b&gt;        8 gavetas.        &lt;br /&gt;
+&lt;b&gt;Tipo de Corrediças:&lt;/b&gt;        Telescópicas.        &lt;br /&gt;
+&lt;b&gt;Tipo de Puxador:&lt;/b&gt;        Alumínio.        &lt;br /&gt;
+&lt;b&gt;Diferenciais:&lt;/b&gt;&lt;br /&gt;                
+- Design moderno.&lt;br /&gt;                
+- 2 gavetões.&lt;br&gt;                
+- Tampo de 25mm MDP.&lt;br /&gt;                
+- Corrediças telescópicas.&lt;br /&gt;                
+- Puxador em alumínio.&lt;br&gt;                
+&lt;b&gt;Sistema de Montagem:&lt;/b&gt;        Cavilhas / Parafusos.        &lt;br /&gt;
+&lt;b&gt;Manual de Montagem:&lt;/b&gt;        Sim.        &lt;br /&gt;
+&lt;b&gt;Complexidade da Montagem:&lt;/b&gt;        Média.        &lt;br /&gt;
+&lt;b&gt;Volumes:&lt;/b&gt;        2 Volumes.        &lt;br /&gt;
+&lt;b&gt;Conteúdo da embalagem:&lt;/b&gt;        1 Cômoda.        &lt;br /&gt;
+&lt;b&gt;Garantia do Fabricante:&lt;/b&gt;        90 dias contra defeito de fabricação.        &lt;br /&gt;
+&lt;b&gt;Montagem:&lt;/b&gt;         Recomendamos que seja feita por um profissional.        &lt;br /&gt;
+&lt;b&gt;Recomendação de Limpeza:&lt;/b&gt;         Pano levemente úmido e detergente neutro.        &lt;br /&gt;
+</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -4460,82 +4598,99 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7901064702738</t>
+          <t>7901064725393</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20037-119</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>COMODA DUBAI INT/DELMONT NATURE/FENDI</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMODA DUBAI INT/DELMONT </t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>COMODA DUBAI INT/DELMONT NATURE/FENDI</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>COMODA DUBAI INT/DELMONT NATURE/FENDI</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>VILA RICA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>COMODA</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>CÔMODAS</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Cômoda Quarto 121cm 8 Gavetas Delmont Nature/Fendi V02 - Mpozenato COD FAB: 20037-119 COR: NATURE/FENDI</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
         <v>2</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>GR 4 PT C/ESP IDEAL/MAYRA NT/CHP/BRISA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>GR 4 PT C/ESP IDEAL/MAYRA</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>GR 4 PT C/ESP IDEAL/MAYRA NT/CHP/BRISA</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GR 4 PT C/ESP IDEAL/MAYRA NT/CHP/BRISA</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>VILA RICA</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>GUARDA ROUPAS</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>GUARDA ROUPAS</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>78</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" t="n">
-        <v>47</v>
-      </c>
-      <c r="W6" t="n">
-        <v>46</v>
-      </c>
-      <c r="X6" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>101</v>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="AB6" t="n">
         <v>90</v>
@@ -4543,8 +4698,10 @@
       <c r="AC6" t="n">
         <v>1000</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3</v>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -4588,7 +4745,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>Guarda Roupa Solteiro 103cm Com Espelho Mayra Nature/Champanhe V02 - Mpozenato</t>
+          <t>Cômoda Quarto 121cm 8 Gavetas Delmont Nature/Fendi V02 - Mpozenato</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -4601,12 +4758,46 @@
           <t>90 dias após o recebimento do produto</t>
         </is>
       </c>
-      <c r="AQ6" t="n">
-        <v>3</v>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>&lt;B&gt;Guarda Roupa Solteiro 103cm Com Espelho Mayra Nature/Champanhe V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;O &lt;B&gt;Guarda Roupa Mayra&lt;/B&gt; é a solução compacta e funcional para quem busca otimizar o espaço sem abrir mão da organização. Com quatro portas, sendo duas &lt;B&gt;Portas Com Espelho&lt;/B&gt;, e duas gavetas, ele oferece amplo espaço interno para organizar roupas, sapatos e outros pertences de maneira eficiente. Suas cincos prateleiras são perfeitas para manter tudo organizado, enquanto o espaço para cabides facilita o acesso rápido às suas peças favoritas. &lt;BR&gt;&lt;BR&gt;Este &lt;B&gt;Guarda Roupa&lt;/B&gt; foi projetado para oferecer praticidade no dia a dia. As gavetas são equipadas com corrediças metálicas, garantindo durabilidade e facilidade de uso, enquanto os puxadores oferecem uma pegada confortável e ergonômica. &lt;BR&gt;&lt;BR&gt;Os pés elevados do guarda roupa protegem o móvel da umidade, aumentando sua vida útil e garantindo uma melhor circulação de ar. Além disso, o design do guarda roupa é pensado para valorizar o ambiente e trazer uma sensação de aconchego e sofisticação ao seu quarto. &lt;BR&gt;&lt;BR&gt;Compacto e altamente funcional, é a escolha perfeita para quem busca praticidade, durabilidade e estilo. Seu design inteligente e detalhado proporciona uma excelente experiência no seu &lt;B&gt;Quarto Solteiro&lt;/B&gt;, mantendo tudo organizado e ao seu alcance com muito mais facilidade. &lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;ESPECIFICAÇÕES&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;Dimensões do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Largura&lt;/B&gt;: 103 cm. &lt;BR&gt;&lt;B&gt;Altura:&lt;/B&gt; 181 cm. &lt;BR&gt;&lt;B&gt;Profundidade:&lt;/B&gt; 40 cm. &lt;BR&gt;&lt;B&gt;Peso:&lt;/B&gt; 46 Kg. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Características do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Material da Estrutura:&lt;/B&gt; MDP. &lt;BR&gt;&lt;B&gt;Espessura das Chapas:&lt;/B&gt; 12mm &lt;BR&gt;&lt;B&gt;Material do Fundo:&lt;/B&gt; MDF 3mm. &lt;BR&gt;&lt;B&gt;Peso Suportado:&lt;/B&gt; 31 kg distribuídos. &lt;BR&gt;&lt;B&gt;Acabamento:&lt;/B&gt; Pintura UV. &lt;BR&gt;&lt;B&gt;Escala de Brilho:&lt;/B&gt; Acetinado/Fosco. &lt;BR&gt;&lt;B&gt;Quantidade de Portas:&lt;/B&gt; 4 Portas. &lt;BR&gt;&lt;B&gt;Material da Dobradiça:&lt;/B&gt; Metal. &lt;BR&gt;&lt;B&gt;Tipo de Porta:&lt;/B&gt; Convencional. &lt;BR&gt;&lt;B&gt;Possui Cabideiros:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Cabideiro:&lt;/B&gt; 1 Cabideiro. &lt;BR&gt;&lt;B&gt;Material do Cabideiro:&lt;/B&gt; Madeira. &lt;BR&gt;&lt;B&gt;Possui Gaveta:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Gavetas:&lt;/B&gt; 2 Gavetas. &lt;BR&gt;&lt;B&gt;Tipo de Corrediças:&lt;/B&gt; Metálicas. &lt;BR&gt;&lt;B&gt;Material do Puxador:&lt;/B&gt; Plástico ABS. &lt;BR&gt;&lt;B&gt;Possui Prateleiras:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Prateleiras:&lt;/B&gt; 5 Prateleiras. &lt;BR&gt;&lt;B&gt;Possui Pés:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Pés:&lt;/B&gt; 4 Pés. &lt;BR&gt;&lt;B&gt;Material dos Pés: &lt;/B&gt;Plástico PVC. &lt;BR&gt;&lt;B&gt;Possui Espelho:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Diferenciais: &lt;/B&gt;&lt;BR&gt;- Prateleiras amplas.&lt;BR&gt;- Corrediças metálicas.&lt;BR&gt;- Desing moderno.&lt;BR&gt;- Portas com dobradiças metálicas.&lt;BR&gt;- Portas com espelho.&lt;BR&gt;&lt;B&gt;Sistema de Montagem:&lt;/B&gt; Cavilhas/Parafusos. &lt;BR&gt;&lt;B&gt;Manual de Montagem:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Complexidade da Montagem:&lt;/B&gt; Média. &lt;BR&gt;&lt;B&gt;Volumes:&lt;/B&gt; 3 Volumes. &lt;BR&gt;&lt;B&gt;Conteúdo da embalagem:&lt;/B&gt; 1 Guarda Roupa. &lt;BR&gt;&lt;B&gt;Garantia do Fabricante:&lt;/B&gt; 90 dias contra defeito de fabricação. &lt;BR&gt;&lt;B&gt;Montagem:&lt;/B&gt; Recomendamos que seja feita por um profissional. &lt;BR&gt;&lt;B&gt;Recomendação de Limpeza:&lt;/B&gt; Utilize pano levemente úmido. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Observações importantes &lt;/B&gt;&lt;BR&gt;- Produto para uso residencial em ambiente interno, não devendo ficar exposto diretamente ao sol, calor e umidades excessivas.&lt;BR&gt;- Pode haver alguma diferença de tonalidade entre a imagem e o produto real, por conta do tratamento de imagens e a calibração de cores do seu monitor.&lt;BR&gt;- As imagens são meramente ilustrativas, não acompanham objetos de decoração e eletrônicos.&lt;BR&gt;- Ao receber a mercadoria, o cliente deve verificar as condições da embalagem, caso haja algum problema não assine o comprovante de recebimento.&lt;BR&gt;- Montagem, desmontagem e outras instalações serão de responsabilidade do cliente. Não nos responsabilizamos, no ato da entrega, por subir escadas/elevadores ou pelo transporte por guincho em apartamentos. Eventuais despesas são de responsabilidade do comprador.&lt;BR&gt;- Confira as dimensões do produto e certifique-se de que passará normalmente por supostos elevadores, portas, escadas e/ou corredores de sua residência.</t>
+          <t xml:space="preserve">&lt;B&gt;Cômoda Quarto 121cm 8 Gavetas Delmont Nature/Fendi V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt; Desenvolvida para ir além do convencional, entrega sofisticação, estilo e presença marcante, elevando a composição do &lt;b&gt;Quarto&lt;/b&gt; com elegância. A &lt;b&gt;Cômoda&lt;/b&gt; moderna e acabamento refinado, ideal para ambientes bem planejados.&lt;br&gt;&lt;br&gt;
+O tampo em MDP de 25mm oferece superfície ampla e resistente para acomodar objetos decorativos ou itens de uso diário. A estrutura em MDF proporciona estabilidade, segurança e excelente durabilidade.&lt;br&gt;&lt;br&gt;
+&lt;b&gt;Cômoda 8 Gavetas&lt;/b&gt;, que garante ótima capacidade de organização no dia a dia. Duas delas são gavetões profundos com fundo reforçado, ideais para peças volumosas e itens maiores.&lt;br&gt;&lt;br&gt;
+As gavetas da &lt;b&gt;Cômoda&lt;/b&gt; possuem corrediças telescópicas, assegurando abertura suave e maior vida útil ao móvel. Já os puxadores em alumínio acrescentam um toque atual e sofisticado, unindo resistência e beleza em cada detalhe. &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;ESPECIFICAÇÕES&lt;/b&gt; &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;Dimensões do Produto&lt;/b&gt;&lt;br /&gt;                
+&lt;b&gt;Largura:&lt;/b&gt;        121 cm.        &lt;br /&gt;
+&lt;b&gt;Altura:&lt;/b&gt;        104 cm.        &lt;br /&gt;
+&lt;b&gt;Profundidade:&lt;/b&gt;        47 cm.        &lt;br /&gt;
+&lt;b&gt;Peso:&lt;/b&gt;        63 Kg.        &lt;br /&gt;
+&lt;br /&gt;                
+&lt;b&gt;Características do Produto&lt;/b&gt;&lt;br /&gt;                
+&lt;b&gt;Material da Estrutura:&lt;/b&gt;        MDF/MDP.        &lt;br /&gt;
+&lt;b&gt;Espessura das Chapas:&lt;/b&gt;        12mm/15mm/25mm.        &lt;br /&gt;
+&lt;b&gt;Peso Suportado:&lt;/b&gt;        28 kg Distribuídos.        &lt;br /&gt;
+&lt;b&gt;Acabamento:&lt;/b&gt;        Pintura UV.        &lt;br /&gt;
+&lt;b&gt;Escala de Brilho:&lt;/b&gt;        Fosco.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Gavetas:&lt;/b&gt;        8 gavetas.        &lt;br /&gt;
+&lt;b&gt;Tipo de Corrediças:&lt;/b&gt;        Telescópicas.        &lt;br /&gt;
+&lt;b&gt;Tipo de Puxador:&lt;/b&gt;        Alumínio.        &lt;br /&gt;
+&lt;b&gt;Diferenciais:&lt;/b&gt;&lt;br /&gt;                
+- Design moderno.&lt;br /&gt;                
+- 2 gavetões.&lt;br&gt;                
+- Tampo de 25mm MDP.&lt;br /&gt;                
+- Corrediças telescópicas.&lt;br /&gt;                
+- Puxador em alumínio.&lt;br&gt;                
+&lt;b&gt;Sistema de Montagem:&lt;/b&gt;        Cavilhas / Parafusos.        &lt;br /&gt;
+&lt;b&gt;Manual de Montagem:&lt;/b&gt;        Sim.        &lt;br /&gt;
+&lt;b&gt;Complexidade da Montagem:&lt;/b&gt;        Média.        &lt;br /&gt;
+&lt;b&gt;Volumes:&lt;/b&gt;        2 Volumes.        &lt;br /&gt;
+&lt;b&gt;Conteúdo da embalagem:&lt;/b&gt;        1 Cômoda.        &lt;br /&gt;
+&lt;b&gt;Garantia do Fabricante:&lt;/b&gt;        90 dias contra defeito de fabricação.        &lt;br /&gt;
+&lt;b&gt;Montagem:&lt;/b&gt;         Recomendamos que seja feita por um profissional.        &lt;br /&gt;
+&lt;b&gt;Recomendação de Limpeza:&lt;/b&gt;         Pano levemente úmido e detergente neutro.        &lt;br /&gt;
+</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -4623,12 +4814,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7901064702745</t>
+          <t>7901064725409</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10091-114</t>
+          <t>10118-119</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4636,22 +4827,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA BRANCO FLEX</t>
+          <t>GUARDA ROUPA DUBAI INF/ZANE NATURE/FENDI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA BRANC</t>
+          <t>GUARDA ROUPA DUBAI INF/ZA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA BRANCO FLEX</t>
+          <t>GUARDA ROUPA DUBAI INF/ZANE NATURE/FENDI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA BRANCO FLEX</t>
+          <t>GUARDA ROUPA DUBAI INF/ZANE NATURE/FENDI</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -4661,16 +4852,18 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>GUARDA ROUPAS</t>
+          <t>GUARDA ROUPA</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>GUARDA ROUPAS</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>74</v>
+          <t>GUARDA ROUPA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Guarda Roupa Casal 164cm Zane Nature/Fendi Flex V02 - Mpozenato COD FAB: 10118-119 COR: NATURE/FENDI</t>
+        </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -4688,22 +4881,32 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>61</v>
-      </c>
-      <c r="W7" t="n">
-        <v>60</v>
-      </c>
-      <c r="X7" t="n">
-        <v>51</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>180</v>
+        <v>3</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="AB7" t="n">
         <v>90</v>
@@ -4711,8 +4914,10 @@
       <c r="AC7" t="n">
         <v>1000</v>
       </c>
-      <c r="AD7" t="n">
-        <v>3</v>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -4756,7 +4961,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>Guarda Roupa Solteiro 154cm Com 6 Portas Mayra Branco Flex V02 - Mpozenato</t>
+          <t>Guarda Roupa Casal 164cm Zane Nature/Fendi Flex V02 - Mpozenato</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -4769,12 +4974,53 @@
           <t>90 dias após o recebimento do produto</t>
         </is>
       </c>
-      <c r="AQ7" t="n">
-        <v>3</v>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>&lt;B&gt;Guarda Roupa Solteiro 154cm Com 6 Portas Mayra Branco Flex V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;O &lt;B&gt;Guarda Roupa Mayra&lt;/B&gt; é a solução compacta e funcional para quem busca otimizar o espaço sem abrir mão da organização. Com seis portas e duas gavetas, ele oferece espaço interno para acomodar suas roupas, sapatos e outros pertences. Suas cincos prateleiras são perfeitas para manter tudo organizado, enquanto o espaço para cabides facilita o acesso rápido às suas peças favoritas. &lt;BR&gt;&lt;BR&gt;Este &lt;B&gt;Guarda Roupa&lt;/B&gt; foi projetado para oferecer praticidade no dia a dia. As gavetas são equipadas com corrediças metálicas, garantindo durabilidade e facilidade de uso, enquanto os puxadores oferecem uma pegada confortável e ergonômica. &lt;BR&gt;&lt;BR&gt;Os pés elevados do guarda roupa protegem o móvel da umidade, aumentando sua vida útil e garantindo uma melhor circulação de ar. Além disso, o design do guarda roupa com vistas flex é pensado para valorizar o ambiente e trazer uma sensação de aconchego e sofisticação ao seu quarto.&lt;BR&gt;&lt;BR&gt;Compacto e altamente funcional, é a escolha perfeita para quem busca praticidade, durabilidade e estilo. Seu design inteligente e detalhado proporciona uma excelente experiência no seu &lt;B&gt;Quarto Solteiro&lt;/B&gt;, mantendo tudo organizado e ao seu alcance com muito mais facilidade. &lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;ESPECIFICAÇÕES&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;Dimensões do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Largura&lt;/B&gt;: 154 cm. &lt;BR&gt;&lt;B&gt;Altura:&lt;/B&gt; 181 cm. &lt;BR&gt;&lt;B&gt;Profundidade:&lt;/B&gt; 40 cm. &lt;BR&gt;&lt;B&gt;Peso:&lt;/B&gt; 59,5Kg. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Características do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Material da Estrutura:&lt;/B&gt; MDP. &lt;BR&gt;&lt;B&gt;Espessura das Chapas:&lt;/B&gt; 12mm &lt;BR&gt;&lt;B&gt;Material do Fundo:&lt;/B&gt; MDF 3mm. &lt;BR&gt;&lt;B&gt;Peso Suportado:&lt;/B&gt; 61 kg distribuídos. &lt;BR&gt;&lt;B&gt;Acabamento:&lt;/B&gt; Pintura UV. &lt;BR&gt;&lt;B&gt;Escala de Brilho:&lt;/B&gt; Acetinado/Fosco. &lt;BR&gt;&lt;B&gt;Quantidade de Portas:&lt;/B&gt; 6 Portas. &lt;BR&gt;&lt;B&gt;Material da Dobradiça:&lt;/B&gt; Metal. &lt;BR&gt;&lt;B&gt;Tipo de Porta:&lt;/B&gt; Convencional. &lt;BR&gt;&lt;B&gt;Possui Cabideiros:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Cabideiro:&lt;/B&gt; 1 Cabideiro. &lt;BR&gt;&lt;B&gt;Material do Cabideiro:&lt;/B&gt; Madeira. &lt;BR&gt;&lt;B&gt;Possui Gaveta:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Gavetas:&lt;/B&gt; 2 Gavetas. &lt;BR&gt;&lt;B&gt;Tipo de Corrediças:&lt;/B&gt; Metálicas. &lt;BR&gt;&lt;B&gt;Material do Puxador:&lt;/B&gt; Plástico ABS. &lt;BR&gt;&lt;B&gt;Possui Prateleiras:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Prateleiras:&lt;/B&gt; 5 Prateleiras. &lt;BR&gt;&lt;B&gt;Possui Pés:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Pés:&lt;/B&gt; 4 Pés. &lt;BR&gt;&lt;B&gt;Material dos Pés: &lt;/B&gt;Plástico PVC. &lt;BR&gt;&lt;B&gt;Possui Espelho:&lt;/B&gt; Não. &lt;BR&gt;&lt;B&gt;Diferenciais: &lt;/B&gt;&lt;BR&gt;- Prateleiras amplas.&lt;BR&gt;- Corrediças metálicas.&lt;BR&gt;- Desing moderno.&lt;BR&gt;- Portas com dobradiça Metálicas.&lt;BR&gt;- Vistas Flex.&lt;BR&gt;&lt;B&gt;Sistema de Montagem:&lt;/B&gt; Cavilhas/Parafusos. &lt;BR&gt;&lt;B&gt;Manual de Montagem:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Complexidade da Montagem:&lt;/B&gt; Média. &lt;BR&gt;&lt;B&gt;Volumes:&lt;/B&gt; 1 Volume. &lt;BR&gt;&lt;B&gt;Conteúdo da embalagem:&lt;/B&gt; 1 Guarda Roupa. &lt;BR&gt;&lt;B&gt;Garantia do Fabricante:&lt;/B&gt; 90 dias contra defeito de fabricação. &lt;BR&gt;&lt;B&gt;Montagem:&lt;/B&gt; Recomendamos que seja feita por um profissional. &lt;BR&gt;&lt;B&gt;Recomendação de Limpeza:&lt;/B&gt; Utilize pano levemente úmido. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Observações importantes &lt;/B&gt;&lt;BR&gt;- Produto para uso residencial em ambiente interno, não devendo ficar exposto diretamente ao sol, calor e umidades excessivas.&lt;BR&gt;- Pode haver alguma diferença de tonalidade entre a imagem e o produto real, por conta do tratamento de imagens e a calibração de cores do seu monitor.&lt;BR&gt;- As imagens são meramente ilustrativas, não acompanham objetos de decoração e eletrônicos.&lt;BR&gt;- Ao receber a mercadoria, o cliente deve verificar as condições da embalagem, caso haja algum problema não assine o comprovante de recebimento.&lt;BR&gt;- Montagem, desmontagem e outras instalações serão de responsabilidade do cliente. Não nos responsabilizamos, no ato da entrega, por subir escadas/elevadores ou pelo transporte por guincho em apartamentos. Eventuais despesas são de responsabilidade do comprador.&lt;BR&gt;- Confira as dimensões do produto e certifique-se de que passará normalmente por supostos elevadores, portas, escadas e/ou corredores de sua residência.</t>
+          <t xml:space="preserve">&lt;B&gt;Guarda Roupa Casal 164cm Zane Nature/Fendi Flex V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt; Ideal para quem busca otimizar ambientes compactos, oferece portas de correr que economizam espaço sem abrir mão da elegância. O &lt;b&gt;Guarda Roupa Casal&lt;/b&gt; apresenta perfil aplicado nas portas, detalhe que valoriza o design e traz modernidade ao &lt;b&gt;Quarto&lt;/b&gt;.&lt;br&gt;&lt;br&gt;
+As portas deslizantes do &lt;b&gt;Guarda Roupa&lt;/b&gt; com pintura dupla face permitem diferentes possibilidades de montagem. O perfil anti-empeno garante estabilidade, firmeza e um deslize suave no uso diário.&lt;br&gt;&lt;br&gt;
+Interna do &lt;b&gt;Guarda Roupa&lt;/b&gt;, conta com corrediças telescópicas nas gavetas, proporcionando abertura suave e maior durabilidade. A estrutura em MDF assegura robustez, resistência e excelente qualidade construtiva.&lt;br&gt;&lt;br&gt;
+Os puxadores em MDF integrados ao design reforçam a estética moderna seu &lt;b&gt;Quarto&lt;/b&gt; e oferecem ergonomia no manuseio. A pintura de alta qualidade valoriza cada detalhe, garantindo acabamento elegante e maior durabilidade ao móvel. &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;ESPECIFICAÇÕES&lt;/b&gt; &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;Dimensões do Produto &lt;/b&gt;&lt;br /&gt;                
+&lt;b&gt;Largura&lt;/b&gt;:        164 cm.        &lt;br /&gt;
+&lt;b&gt;Altura:&lt;/b&gt;        235 cm.        &lt;br /&gt;
+&lt;b&gt;Profundidade:&lt;/b&gt;        56 cm.        &lt;br /&gt;
+&lt;b&gt;Peso:&lt;/b&gt;        131 Kg.        &lt;br /&gt;
+&lt;br /&gt;                
+&lt;b&gt;Características do Produto &lt;/b&gt;&lt;br /&gt;                
+&lt;b&gt;Material da Estrutura:&lt;/b&gt;        MDF.        &lt;br /&gt;
+&lt;b&gt;Espessura das Chapas:&lt;/b&gt;        12mm/15mm.        &lt;br /&gt;
+&lt;b&gt;Peso suportado:&lt;/b&gt;        62 kg distribuídos.        &lt;br /&gt;
+&lt;b&gt;Acabamento:&lt;/b&gt;        Pintura UV.        &lt;br /&gt;
+&lt;b&gt;Escala de Brilho:&lt;/b&gt;        Fosco.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Portas:&lt;/b&gt;        2 portas.        &lt;br /&gt;
+&lt;b&gt;Tipo de Porta:&lt;/b&gt;        Deslizante.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Cabideiro:&lt;/b&gt;        1 cabideiro.        &lt;br /&gt;
+&lt;b&gt;Material do Cabideiro:&lt;/b&gt;        Alumínio.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Gavetas:&lt;/b&gt;        3 gavetas.        &lt;br /&gt;
+&lt;b&gt;Tipo de Corrediças:&lt;/b&gt;        Telescópicas.        &lt;br /&gt;
+&lt;b&gt;Material do Puxador:&lt;/b&gt;        MDF.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Prateleiras:&lt;/b&gt;        10 prateleiras.        &lt;br /&gt;
+&lt;b&gt;Material dos Pés:&lt;/b&gt;        PVC.        &lt;br /&gt;
+&lt;b&gt;Diferenciais: &lt;/b&gt;&lt;br /&gt;                
+- Design moderno.&lt;br /&gt;                
+- Trilho inferior em alumínio.&lt;br /&gt;                
+- Perfil anti empeno nas portas.&lt;br /&gt;                
+- Corrediças telescópicas.&lt;br /&gt;                
+- Puxador em MDF.&lt;br /&gt;                
+- Pés PVC.&lt;br /&gt;                
+&lt;b&gt;Sistema de Montagem:&lt;/b&gt;        Cavilhas / Parafusos.        &lt;br /&gt;
+&lt;b&gt;Manual de Montagem:&lt;/b&gt;        Sim.        &lt;br /&gt;
+&lt;b&gt;Complexidade da Montagem:&lt;/b&gt;        Média.        &lt;br /&gt;
+&lt;b&gt;Volumes:&lt;/b&gt;        3 Volumes.        &lt;br /&gt;
+&lt;b&gt;Conteúdo da embalagem:&lt;/b&gt;        1 Guarda Roupa.        &lt;br /&gt;
+&lt;b&gt;Garantia do Fabricante:&lt;/b&gt;        90 dias contra defeito de fabricação.        &lt;br /&gt;
+&lt;b&gt;Montagem:&lt;/b&gt;        Recomendamos que seja feita por um profissional.        &lt;br /&gt;
+&lt;b&gt;Recomendação de Limpeza:&lt;/b&gt;        Utilize pano levemente úmido.        &lt;br /&gt;
+</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -4791,12 +5037,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7901064702752</t>
+          <t>7901064725416</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10091-91</t>
+          <t>10118-120</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4804,22 +5050,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA IMBUIA/CHP</t>
+          <t>GUARDA ROUPA DUBAI INF/ZANE NT/CRM/ALS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA IMBUI</t>
+          <t>GUARDA ROUPA DUBAI INF/ZA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA IMBUIA/CHP</t>
+          <t>GUARDA ROUPA DUBAI INF/ZANE NT/CRM/ALS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA IMBUIA/CHP</t>
+          <t>GUARDA ROUPA DUBAI INF/ZANE NT/CRM/ALS</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -4829,16 +5075,18 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>GUARDA ROUPAS</t>
+          <t>GUARDA ROUPA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>GUARDA ROUPAS</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>79</v>
+          <t>GUARDA ROUPA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Guarda Roupa Casal 164cm Zane Nature/Camarim/Alasca Flex V02 - Mpozenato COD FAB: 10118-120 COR: NATURE/CAMARIM/ALASCA</t>
+        </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -4856,22 +5104,32 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>61</v>
-      </c>
-      <c r="W8" t="n">
-        <v>60</v>
-      </c>
-      <c r="X8" t="n">
-        <v>51</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>180</v>
+        <v>3</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="AB8" t="n">
         <v>90</v>
@@ -4879,8 +5137,10 @@
       <c r="AC8" t="n">
         <v>1000</v>
       </c>
-      <c r="AD8" t="n">
-        <v>3</v>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -4924,7 +5184,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>Guarda Roupa Solteiro 154cm Com 6 Portas Mayra Imbuia/Champanhe V02 - Mpozenato</t>
+          <t>Guarda Roupa Casal 164cm Zane Nature/Camarim/Alasca Flex V02 - Mpozenato</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4937,12 +5197,53 @@
           <t>90 dias após o recebimento do produto</t>
         </is>
       </c>
-      <c r="AQ8" t="n">
-        <v>3</v>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>&lt;B&gt;Guarda Roupa Solteiro 154cm Com 6 Portas Mayra Imbuia/Champanhe V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;O &lt;B&gt;Guarda Roupa Mayra&lt;/B&gt; é a solução compacta e funcional para quem busca otimizar o espaço sem abrir mão da organização. Com seis portas e duas gavetas, ele oferece espaço interno para acomodar suas roupas, sapatos e outros pertences. Suas cincos prateleiras são perfeitas para manter tudo organizado, enquanto o espaço para cabides facilita o acesso rápido às suas peças favoritas. &lt;BR&gt;&lt;BR&gt;Este &lt;B&gt;Guarda Roupa&lt;/B&gt; foi projetado para oferecer praticidade no dia a dia. As gavetas são equipadas com corrediças metálicas, garantindo durabilidade e facilidade de uso, enquanto os puxadores oferecem uma pegada confortável e ergonômica. &lt;BR&gt;&lt;BR&gt;Os pés elevados do guarda roupa protegem o móvel da umidade, aumentando sua vida útil e garantindo uma melhor circulação de ar. Além disso, o design do guarda roupa é pensado para valorizar o ambiente e trazer uma sensação de aconchego e sofisticação ao seu quarto. &lt;BR&gt;&lt;BR&gt;Compacto e altamente funcional, é a escolha perfeita para quem busca praticidade, durabilidade e estilo. Seu design inteligente e detalhado proporciona uma excelente experiência no seu &lt;B&gt;Quarto Solteiro&lt;/B&gt;, mantendo tudo organizado e ao seu alcance com muito mais facilidade. &lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;ESPECIFICAÇÕES&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;Dimensões do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Largura&lt;/B&gt;: 154 cm. &lt;BR&gt;&lt;B&gt;Altura:&lt;/B&gt; 181 cm. &lt;BR&gt;&lt;B&gt;Profundidade:&lt;/B&gt; 40 cm. &lt;BR&gt;&lt;B&gt;Peso:&lt;/B&gt; 59,5Kg. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Características do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Material da Estrutura:&lt;/B&gt; MDP. &lt;BR&gt;&lt;B&gt;Espessura das Chapas:&lt;/B&gt; 12mm &lt;BR&gt;&lt;B&gt;Material do Fundo:&lt;/B&gt; MDF 3mm. &lt;BR&gt;&lt;B&gt;Peso Suportado:&lt;/B&gt; 61 kg distribuídos. &lt;BR&gt;&lt;B&gt;Acabamento:&lt;/B&gt; Pintura UV. &lt;BR&gt;&lt;B&gt;Escala de Brilho:&lt;/B&gt; Acetinado/Fosco. &lt;BR&gt;&lt;B&gt;Quantidade de Portas:&lt;/B&gt; 6 Portas. &lt;BR&gt;&lt;B&gt;Material da Dobradiça:&lt;/B&gt; Metal. &lt;BR&gt;&lt;B&gt;Tipo de Porta:&lt;/B&gt; Convencional. &lt;BR&gt;&lt;B&gt;Possui Cabideiros:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Cabideiro:&lt;/B&gt; 1 Cabideiro. &lt;BR&gt;&lt;B&gt;Material do Cabideiro:&lt;/B&gt; Madeira. &lt;BR&gt;&lt;B&gt;Possui Gaveta:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Gavetas:&lt;/B&gt; 2 Gavetas. &lt;BR&gt;&lt;B&gt;Tipo de Corrediças:&lt;/B&gt; Metálicas. &lt;BR&gt;&lt;B&gt;Material do Puxador:&lt;/B&gt; Plástico ABS. &lt;BR&gt;&lt;B&gt;Possui Prateleiras:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Prateleiras:&lt;/B&gt; 5 Prateleiras. &lt;BR&gt;&lt;B&gt;Possui Pés:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Pés:&lt;/B&gt; 4 Pés. &lt;BR&gt;&lt;B&gt;Material dos Pés: &lt;/B&gt;Plástico PVC. &lt;BR&gt;&lt;B&gt;Possui Espelho:&lt;/B&gt; Não. &lt;BR&gt;&lt;B&gt;Diferenciais: &lt;/B&gt;&lt;BR&gt;- Prateleiras amplas.&lt;BR&gt;- Corrediças metálicas.&lt;BR&gt;- Desing moderno.&lt;BR&gt;- Portas com dobradiça Metálicas.&lt;BR&gt;&lt;B&gt;Sistema de Montagem:&lt;/B&gt; Cavilhas/Parafusos. &lt;BR&gt;&lt;B&gt;Manual de Montagem:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Complexidade da Montagem:&lt;/B&gt; Média. &lt;BR&gt;&lt;B&gt;Volumes:&lt;/B&gt; 1 Volume. &lt;BR&gt;&lt;B&gt;Conteúdo da embalagem:&lt;/B&gt; 1 Guarda Roupa. &lt;BR&gt;&lt;B&gt;Garantia do Fabricante:&lt;/B&gt; 90 dias contra defeito de fabricação. &lt;BR&gt;&lt;B&gt;Montagem:&lt;/B&gt; Recomendamos que seja feita por um profissional. &lt;BR&gt;&lt;B&gt;Recomendação de Limpeza:&lt;/B&gt; Utilize pano levemente úmido. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Observações importantes &lt;/B&gt;&lt;BR&gt;- Produto para uso residencial em ambiente interno, não devendo ficar exposto diretamente ao sol, calor e umidades excessivas.&lt;BR&gt;- Pode haver alguma diferença de tonalidade entre a imagem e o produto real, por conta do tratamento de imagens e a calibração de cores do seu monitor.&lt;BR&gt;- As imagens são meramente ilustrativas, não acompanham objetos de decoração e eletrônicos.&lt;BR&gt;- Ao receber a mercadoria, o cliente deve verificar as condições da embalagem, caso haja algum problema não assine o comprovante de recebimento.&lt;BR&gt;- Montagem, desmontagem e outras instalações serão de responsabilidade do cliente. Não nos responsabilizamos, no ato da entrega, por subir escadas/elevadores ou pelo transporte por guincho em apartamentos. Eventuais despesas são de responsabilidade do comprador.&lt;BR&gt;- Confira as dimensões do produto e certifique-se de que passará normalmente por supostos elevadores, portas, escadas e/ou corredores de sua residência.</t>
+          <t xml:space="preserve">&lt;B&gt;Guarda Roupa Casal 164cm Zane Nature/Camarim/Alasca Flex V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt; Ideal para quem busca otimizar ambientes compactos, oferece portas de correr que economizam espaço sem abrir mão da elegância. O &lt;b&gt;Guarda Roupa Casal&lt;/b&gt; apresenta perfil aplicado nas portas, detalhe que valoriza o design e traz modernidade ao &lt;b&gt;Quarto&lt;/b&gt;.&lt;br&gt;&lt;br&gt;
+As portas deslizantes do &lt;b&gt;Guarda Roupa&lt;/b&gt; com pintura dupla face permitem diferentes possibilidades de montagem. O perfil anti-empeno garante estabilidade, firmeza e um deslize suave no uso diário.&lt;br&gt;&lt;br&gt;
+Interna do &lt;b&gt;Guarda Roupa&lt;/b&gt;, conta com corrediças telescópicas nas gavetas, proporcionando abertura suave e maior durabilidade. A estrutura em MDF assegura robustez, resistência e excelente qualidade construtiva.&lt;br&gt;&lt;br&gt;
+Os puxadores em MDF integrados ao design reforçam a estética moderna seu &lt;b&gt;Quarto&lt;/b&gt; e oferecem ergonomia no manuseio. A pintura de alta qualidade valoriza cada detalhe, garantindo acabamento elegante e maior durabilidade ao móvel. &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;ESPECIFICAÇÕES&lt;/b&gt; &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;Dimensões do Produto &lt;/b&gt;&lt;br /&gt;                
+&lt;b&gt;Largura&lt;/b&gt;:        164 cm.        &lt;br /&gt;
+&lt;b&gt;Altura:&lt;/b&gt;        235 cm.        &lt;br /&gt;
+&lt;b&gt;Profundidade:&lt;/b&gt;        56 cm.        &lt;br /&gt;
+&lt;b&gt;Peso:&lt;/b&gt;        131 Kg.        &lt;br /&gt;
+&lt;br /&gt;                
+&lt;b&gt;Características do Produto &lt;/b&gt;&lt;br /&gt;                
+&lt;b&gt;Material da Estrutura:&lt;/b&gt;        MDF.        &lt;br /&gt;
+&lt;b&gt;Espessura das Chapas:&lt;/b&gt;        12mm/15mm.        &lt;br /&gt;
+&lt;b&gt;Peso suportado:&lt;/b&gt;        62 kg distribuídos.        &lt;br /&gt;
+&lt;b&gt;Acabamento:&lt;/b&gt;        Pintura UV.        &lt;br /&gt;
+&lt;b&gt;Escala de Brilho:&lt;/b&gt;        Fosco.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Portas:&lt;/b&gt;        2 portas.        &lt;br /&gt;
+&lt;b&gt;Tipo de Porta:&lt;/b&gt;        Deslizante.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Cabideiro:&lt;/b&gt;        1 cabideiro.        &lt;br /&gt;
+&lt;b&gt;Material do Cabideiro:&lt;/b&gt;        Alumínio.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Gavetas:&lt;/b&gt;        3 gavetas.        &lt;br /&gt;
+&lt;b&gt;Tipo de Corrediças:&lt;/b&gt;        Telescópicas.        &lt;br /&gt;
+&lt;b&gt;Material do Puxador:&lt;/b&gt;        MDF.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Prateleiras:&lt;/b&gt;        10 prateleiras.        &lt;br /&gt;
+&lt;b&gt;Material dos Pés:&lt;/b&gt;        PVC.        &lt;br /&gt;
+&lt;b&gt;Diferenciais: &lt;/b&gt;&lt;br /&gt;                
+- Design moderno.&lt;br /&gt;                
+- Trilho Inferior em alumínio.&lt;br /&gt;                
+- Perfil anti empeno nas portas.&lt;br /&gt;                
+- Corrediças telescópicas.&lt;br /&gt;                
+- Puxador em MDF.&lt;br /&gt;                
+- Pés PVC.&lt;br /&gt;                
+&lt;b&gt;Sistema de Montagem:&lt;/b&gt;        Cavilhas / Parafusos.        &lt;br /&gt;
+&lt;b&gt;Manual de Montagem:&lt;/b&gt;        Sim.        &lt;br /&gt;
+&lt;b&gt;Complexidade da Montagem:&lt;/b&gt;        Média.        &lt;br /&gt;
+&lt;b&gt;Volumes:&lt;/b&gt;        3 Volumes.        &lt;br /&gt;
+&lt;b&gt;Conteúdo da embalagem:&lt;/b&gt;        1 Guarda Roupa.        &lt;br /&gt;
+&lt;b&gt;Garantia do Fabricante:&lt;/b&gt;        90 dias contra defeito de fabricação.        &lt;br /&gt;
+&lt;b&gt;Montagem:&lt;/b&gt;        Recomendamos que seja feita por um profissional.        &lt;br /&gt;
+&lt;b&gt;Recomendação de Limpeza:&lt;/b&gt;        Utilize pano levemente úmido.        &lt;br /&gt;
+</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4959,12 +5260,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7901064702769</t>
+          <t>7901064725423</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10091-80</t>
+          <t>10119-129</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4972,22 +5273,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA IMBUIA</t>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/ALS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA IMBUI</t>
+          <t>GUARDA ROUPA DUBAI OUR/VO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA IMBUIA</t>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/ALS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA IMBUIA</t>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/ALS</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4997,16 +5298,18 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>GUARDA ROUPAS</t>
+          <t>GUARDA ROUPA</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>GUARDA ROUPAS</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>69</v>
+          <t>GUARDA ROUPA</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Guarda Roupa Casal 260cm Vidro Reflecta Vonn Nature/Alasca V02 - Mpozenato COD FAB: 10119-129 COR: NATURE/ALASCA</t>
+        </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -5024,22 +5327,32 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>61</v>
-      </c>
-      <c r="W9" t="n">
-        <v>60</v>
-      </c>
-      <c r="X9" t="n">
-        <v>51</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>180</v>
+        <v>6</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="AB9" t="n">
         <v>90</v>
@@ -5047,8 +5360,10 @@
       <c r="AC9" t="n">
         <v>1000</v>
       </c>
-      <c r="AD9" t="n">
-        <v>3</v>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -5092,7 +5407,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>Guarda Roupa Solteiro 154cm Com 6 Portas Mayra Imbuia V02 - Mpozenato</t>
+          <t>Guarda Roupa Casal 260cm Vidro Reflecta Vonn Nature/Alasca V02 - Mpozenato</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -5105,12 +5420,53 @@
           <t>90 dias após o recebimento do produto</t>
         </is>
       </c>
-      <c r="AQ9" t="n">
-        <v>3</v>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>&lt;B&gt;Guarda Roupa Solteiro 154cm Com 6 Portas Mayra Imbuia V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;O &lt;B&gt;Guarda Roupa Mayra&lt;/B&gt; é a solução compacta e funcional para quem busca otimizar o espaço sem abrir mão da organização. Com seis portas e duas gavetas, ele oferece espaço interno para acomodar suas roupas, sapatos e outros pertences. Suas cincos prateleiras são perfeitas para manter tudo organizado, enquanto o espaço para cabides facilita o acesso rápido às suas peças favoritas. &lt;BR&gt;&lt;BR&gt;Este &lt;B&gt;Guarda Roupa&lt;/B&gt; foi projetado para oferecer praticidade no dia a dia. As gavetas são equipadas com corrediças metálicas, garantindo durabilidade e facilidade de uso, enquanto os puxadores oferecem uma pegada confortável e ergonômica. &lt;BR&gt;&lt;BR&gt;Os pés elevados do guarda roupa protegem o móvel da umidade, aumentando sua vida útil e garantindo uma melhor circulação de ar. Além disso, o design do guarda roupa é pensado para valorizar o ambiente e trazer uma sensação de aconchego e sofisticação ao seu quarto. &lt;BR&gt;&lt;BR&gt;Compacto e altamente funcional, é a escolha perfeita para quem busca praticidade, durabilidade e estilo. Seu design inteligente e detalhado proporciona uma excelente experiência no seu &lt;B&gt;Quarto Solteiro&lt;/B&gt;, mantendo tudo organizado e ao seu alcance com muito mais facilidade. &lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;ESPECIFICAÇÕES&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;Dimensões do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Largura&lt;/B&gt;: 154 cm. &lt;BR&gt;&lt;B&gt;Altura:&lt;/B&gt; 181 cm. &lt;BR&gt;&lt;B&gt;Profundidade:&lt;/B&gt; 40 cm. &lt;BR&gt;&lt;B&gt;Peso:&lt;/B&gt; 59,5Kg. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Características do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Material da Estrutura:&lt;/B&gt; MDP. &lt;BR&gt;&lt;B&gt;Espessura das Chapas:&lt;/B&gt; 12mm &lt;BR&gt;&lt;B&gt;Material do Fundo:&lt;/B&gt; MDF 3mm. &lt;BR&gt;&lt;B&gt;Peso Suportado:&lt;/B&gt; 61 kg distribuídos. &lt;BR&gt;&lt;B&gt;Acabamento:&lt;/B&gt; Pintura UV. &lt;BR&gt;&lt;B&gt;Escala de Brilho:&lt;/B&gt; Acetinado/Fosco. &lt;BR&gt;&lt;B&gt;Quantidade de Portas:&lt;/B&gt; 6 Portas. &lt;BR&gt;&lt;B&gt;Material da Dobradiça:&lt;/B&gt; Metal. &lt;BR&gt;&lt;B&gt;Tipo de Porta:&lt;/B&gt; Convencional. &lt;BR&gt;&lt;B&gt;Possui Cabideiros:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Cabideiro:&lt;/B&gt; 1 Cabideiro. &lt;BR&gt;&lt;B&gt;Material do Cabideiro:&lt;/B&gt; Madeira. &lt;BR&gt;&lt;B&gt;Possui Gaveta:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Gavetas:&lt;/B&gt; 2 Gavetas. &lt;BR&gt;&lt;B&gt;Tipo de Corrediças:&lt;/B&gt; Metálicas. &lt;BR&gt;&lt;B&gt;Material do Puxador:&lt;/B&gt; Plástico ABS. &lt;BR&gt;&lt;B&gt;Possui Prateleiras:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Prateleiras:&lt;/B&gt; 5 Prateleiras. &lt;BR&gt;&lt;B&gt;Possui Pés:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Pés:&lt;/B&gt; 4 Pés. &lt;BR&gt;&lt;B&gt;Material dos Pés: &lt;/B&gt;Plástico PVC. &lt;BR&gt;&lt;B&gt;Possui Espelho:&lt;/B&gt; Não. &lt;BR&gt;&lt;B&gt;Diferenciais: &lt;/B&gt;&lt;BR&gt;- Prateleiras amplas.&lt;BR&gt;- Corrediças metálicas.&lt;BR&gt;- Desing moderno.&lt;BR&gt;- Portas com dobradiça Metálicas.&lt;BR&gt;&lt;B&gt;Sistema de Montagem:&lt;/B&gt; Cavilhas/Parafusos. &lt;BR&gt;&lt;B&gt;Manual de Montagem:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Complexidade da Montagem:&lt;/B&gt; Média. &lt;BR&gt;&lt;B&gt;Volumes:&lt;/B&gt; 1 Volume. &lt;BR&gt;&lt;B&gt;Conteúdo da embalagem:&lt;/B&gt; 1 Guarda Roupa. &lt;BR&gt;&lt;B&gt;Garantia do Fabricante:&lt;/B&gt; 90 dias contra defeito de fabricação. &lt;BR&gt;&lt;B&gt;Montagem:&lt;/B&gt; Recomendamos que seja feita por um profissional. &lt;BR&gt;&lt;B&gt;Recomendação de Limpeza:&lt;/B&gt; Utilize pano levemente úmido. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Observações importantes &lt;/B&gt;&lt;BR&gt;- Produto para uso residencial em ambiente interno, não devendo ficar exposto diretamente ao sol, calor e umidades excessivas.&lt;BR&gt;- Pode haver alguma diferença de tonalidade entre a imagem e o produto real, por conta do tratamento de imagens e a calibração de cores do seu monitor.&lt;BR&gt;- As imagens são meramente ilustrativas, não acompanham objetos de decoração e eletrônicos.&lt;BR&gt;- Ao receber a mercadoria, o cliente deve verificar as condições da embalagem, caso haja algum problema não assine o comprovante de recebimento.&lt;BR&gt;- Montagem, desmontagem e outras instalações serão de responsabilidade do cliente. Não nos responsabilizamos, no ato da entrega, por subir escadas/elevadores ou pelo transporte por guincho em apartamentos. Eventuais despesas são de responsabilidade do comprador.&lt;BR&gt;- Confira as dimensões do produto e certifique-se de que passará normalmente por supostos elevadores, portas, escadas e/ou corredores de sua residência.</t>
+          <t xml:space="preserve">&lt;B&gt;Guarda Roupa Casal 260cm Vidro Reflecta Vonn Nature/Alasca V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt; Desenvolvido para entregar glamour, requinte e sofisticação, eleva o padrão estético e funcional do quarto com presença marcante. O destaque do &lt;b&gt;Guarda Roupa&lt;/b&gt; fica por conta das portas com vidro reflecta, que proporcionam brilho, elegância e um toque contemporâneo ao &lt;b&gt;Quarto&lt;/b&gt;.&lt;br&gt;&lt;br&gt;
+A organização é favorecida pela divisão interna inteligente, pensada para acomodar roupas, acessórios e objetos pessoais com praticidade. Conta ainda com 6 portas com dobradiças com amortecimento, garantindo fechamento suave, silencioso e maior durabilidade no &lt;b&gt;Guarda Roupa&lt;/b&gt;.&lt;br&gt;&lt;br&gt;
+O &lt;b&gt;Guarda Roupa&lt;/b&gt; possui 4 gavetas com corrediças telescópicas, que oferecem abertura suave e excelente resistência no uso diário. A estrutura em MDF assegura robustez, estabilidade e qualidade superior ao móvel.&lt;br&gt;&lt;br&gt;
+Os puxadores em alumínio reforçam o acabamento premium e agregam ainda mais sofisticação ao design do seu &lt;b&gt;Quarto&lt;/b&gt;. Já os pés resistentes garantem firmeza, sustentação e segurança para o uso contínuo. &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;ESPECIFICAÇÕES&lt;/b&gt; &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;Dimensões do Produto &lt;/b&gt;&lt;br /&gt;                
+&lt;b&gt;Largura&lt;/b&gt;:        260 cm.        &lt;br /&gt;
+&lt;b&gt;Altura:&lt;/b&gt;        235 cm.        &lt;br /&gt;
+&lt;b&gt;Profundidade:&lt;/b&gt;        56 cm.        &lt;br /&gt;
+&lt;b&gt;Peso:&lt;/b&gt;        200 Kg.        &lt;br /&gt;
+&lt;br /&gt;                
+&lt;b&gt;Características do Produto &lt;/b&gt;&lt;br /&gt;                
+&lt;b&gt;Material da Estrutura:&lt;/b&gt;        MDF.        &lt;br /&gt;
+&lt;b&gt;Espessura das Chapas:&lt;/b&gt;        15mm.        &lt;br /&gt;
+&lt;b&gt;Peso suportado:&lt;/b&gt;        72 kg distribuídos.        &lt;br /&gt;
+&lt;b&gt;Acabamento:&lt;/b&gt;        Pintura UV.        &lt;br /&gt;
+&lt;b&gt;Escala de Brilho:&lt;/b&gt;        Fosco.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Portas:&lt;/b&gt;        6 portas.        &lt;br /&gt;
+&lt;b&gt;Tipo de Porta:&lt;/b&gt;        Convencional.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Cabideiro:&lt;/b&gt;        3 cabideiros.        &lt;br /&gt;
+&lt;b&gt;Material do Cabideiro:&lt;/b&gt;        Alumínio.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Gavetas:&lt;/b&gt;        4 gavetas.        &lt;br /&gt;
+&lt;b&gt;Tipo de Corrediças:&lt;/b&gt;        Telescópicas.        &lt;br /&gt;
+&lt;b&gt;Material do Puxador:&lt;/b&gt;        Alumínio.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Prateleiras:&lt;/b&gt;        10 prateleiras.        &lt;br /&gt;
+&lt;b&gt;Material dos Pés:&lt;/b&gt;        PVC.        &lt;br /&gt;
+&lt;b&gt;Diferenciais: &lt;/b&gt;&lt;br /&gt;                
+- Design moderno.&lt;br /&gt;                
+- Portas de vidros reflecta.&lt;br /&gt;                
+- Corrediças telescópicas.&lt;br /&gt;                
+- Puxador em alumínio.&lt;br /&gt;                
+- Pés PVC.&lt;br /&gt;                
+- Cabideiros em alumínio.&lt;br /&gt;                
+&lt;b&gt;Sistema de Montagem:&lt;/b&gt;        Cavilhas / Parafusos.        &lt;br /&gt;
+&lt;b&gt;Manual de Montagem:&lt;/b&gt;        Sim.        &lt;br /&gt;
+&lt;b&gt;Complexidade da Montagem:&lt;/b&gt;        Alta.        &lt;br /&gt;
+&lt;b&gt;Volumes:&lt;/b&gt;        6 Volumes.        &lt;br /&gt;
+&lt;b&gt;Conteúdo da embalagem:&lt;/b&gt;        1 Guarda Roupa.        &lt;br /&gt;
+&lt;b&gt;Garantia do Fabricante:&lt;/b&gt;        90 dias contra defeito de fabricação.        &lt;br /&gt;
+&lt;b&gt;Montagem:&lt;/b&gt;        Recomendamos que seja feita por um profissional.        &lt;br /&gt;
+&lt;b&gt;Recomendação de Limpeza:&lt;/b&gt;        Utilize pano levemente úmido.        &lt;br /&gt;
+</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -5127,12 +5483,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7901064702776</t>
+          <t>7901064725430</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10091-127</t>
+          <t>10119-130</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5140,22 +5496,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA NT/CHP/BRISA</t>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/FEN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA NT/CH</t>
+          <t>GUARDA ROUPA DUBAI OUR/VO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA NT/CHP/BRISA</t>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/FEN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA NT/CHP/BRISA</t>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/FEN</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -5165,16 +5521,18 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>GUARDA ROUPAS</t>
+          <t>GUARDA ROUPA</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>GUARDA ROUPAS</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>79</v>
+          <t>GUARDA ROUPA</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Guarda Roupa Casal 260cm Vidro Reflecta Vonn Nature/Fendi V02 - Mpozenato COD FAB: 10119-130 COR: NATURE/FENDI</t>
+        </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -5192,22 +5550,32 @@
         </is>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>61</v>
-      </c>
-      <c r="W10" t="n">
-        <v>60</v>
-      </c>
-      <c r="X10" t="n">
-        <v>51</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>180</v>
+        <v>6</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="AB10" t="n">
         <v>90</v>
@@ -5215,8 +5583,10 @@
       <c r="AC10" t="n">
         <v>1000</v>
       </c>
-      <c r="AD10" t="n">
-        <v>3</v>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -5260,7 +5630,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>Guarda Roupa Solteiro 154cm Com 6 Portas Mayra Nature/Champanhe V02 - Mpozenato</t>
+          <t>Guarda Roupa Casal 260cm Vidro Reflecta Vonn Nature/Fendi V02 - Mpozenato</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5273,12 +5643,53 @@
           <t>90 dias após o recebimento do produto</t>
         </is>
       </c>
-      <c r="AQ10" t="n">
-        <v>3</v>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>&lt;B&gt;Guarda Roupa Solteiro 154cm Com 6 Portas Mayra Nature/Champanhe V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;O &lt;B&gt;Guarda Roupa Mayra&lt;/B&gt; é a solução compacta e funcional para quem busca otimizar o espaço sem abrir mão da organização. Com seis portas e duas gavetas, ele oferece espaço interno para acomodar suas roupas, sapatos e outros pertences. Suas cincos prateleiras são perfeitas para manter tudo organizado, enquanto o espaço para cabides facilita o acesso rápido às suas peças favoritas. &lt;BR&gt;&lt;BR&gt;Este &lt;B&gt;Guarda Roupa&lt;/B&gt; foi projetado para oferecer praticidade no dia a dia. As gavetas são equipadas com corrediças metálicas, garantindo durabilidade e facilidade de uso, enquanto os puxadores oferecem uma pegada confortável e ergonômica. &lt;BR&gt;&lt;BR&gt;Os pés elevados do guarda roupa protegem o móvel da umidade, aumentando sua vida útil e garantindo uma melhor circulação de ar. Além disso, o design do guarda roupa é pensado para valorizar o ambiente e trazer uma sensação de aconchego e sofisticação ao seu quarto. &lt;BR&gt;&lt;BR&gt;Compacto e altamente funcional, é a escolha perfeita para quem busca praticidade, durabilidade e estilo. Seu design inteligente e detalhado proporciona uma excelente experiência no seu &lt;B&gt;Quarto Solteiro&lt;/B&gt;, mantendo tudo organizado e ao seu alcance com muito mais facilidade. &lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;ESPECIFICAÇÕES&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;Dimensões do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Largura&lt;/B&gt;: 154 cm. &lt;BR&gt;&lt;B&gt;Altura:&lt;/B&gt; 181 cm. &lt;BR&gt;&lt;B&gt;Profundidade:&lt;/B&gt; 40 cm. &lt;BR&gt;&lt;B&gt;Peso:&lt;/B&gt; 59,5Kg. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Características do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Material da Estrutura:&lt;/B&gt; MDP. &lt;BR&gt;&lt;B&gt;Espessura das Chapas:&lt;/B&gt; 12mm &lt;BR&gt;&lt;B&gt;Material do Fundo:&lt;/B&gt; MDF 3mm. &lt;BR&gt;&lt;B&gt;Peso Suportado:&lt;/B&gt; 61 kg distribuídos. &lt;BR&gt;&lt;B&gt;Acabamento:&lt;/B&gt; Pintura UV. &lt;BR&gt;&lt;B&gt;Escala de Brilho:&lt;/B&gt; Acetinado/Fosco. &lt;BR&gt;&lt;B&gt;Quantidade de Portas:&lt;/B&gt; 6 Portas. &lt;BR&gt;&lt;B&gt;Material da Dobradiça:&lt;/B&gt; Metal. &lt;BR&gt;&lt;B&gt;Tipo de Porta:&lt;/B&gt; Convencional. &lt;BR&gt;&lt;B&gt;Possui Cabideiros:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Cabideiro:&lt;/B&gt; 1 Cabideiro. &lt;BR&gt;&lt;B&gt;Material do Cabideiro:&lt;/B&gt; Madeira. &lt;BR&gt;&lt;B&gt;Possui Gaveta:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Gavetas:&lt;/B&gt; 2 Gavetas. &lt;BR&gt;&lt;B&gt;Tipo de Corrediças:&lt;/B&gt; Metálicas. &lt;BR&gt;&lt;B&gt;Material do Puxador:&lt;/B&gt; Plástico ABS. &lt;BR&gt;&lt;B&gt;Possui Prateleiras:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Prateleiras:&lt;/B&gt; 5 Prateleiras. &lt;BR&gt;&lt;B&gt;Possui Pés:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Pés:&lt;/B&gt; 4 Pés. &lt;BR&gt;&lt;B&gt;Material dos Pés: &lt;/B&gt;Plástico PVC. &lt;BR&gt;&lt;B&gt;Possui Espelho:&lt;/B&gt; Não. &lt;BR&gt;&lt;B&gt;Diferenciais: &lt;/B&gt;&lt;BR&gt;- Prateleiras amplas.&lt;BR&gt;- Corrediças metálicas.&lt;BR&gt;- Desing moderno.&lt;BR&gt;- Portas com dobradiça Metálicas.&lt;BR&gt;&lt;B&gt;Sistema de Montagem:&lt;/B&gt; Cavilhas/Parafusos. &lt;BR&gt;&lt;B&gt;Manual de Montagem:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Complexidade da Montagem:&lt;/B&gt; Média. &lt;BR&gt;&lt;B&gt;Volumes:&lt;/B&gt; 1 Volume. &lt;BR&gt;&lt;B&gt;Conteúdo da embalagem:&lt;/B&gt; 1 Guarda Roupa. &lt;BR&gt;&lt;B&gt;Garantia do Fabricante:&lt;/B&gt; 90 dias contra defeito de fabricação. &lt;BR&gt;&lt;B&gt;Montagem:&lt;/B&gt; Recomendamos que seja feita por um profissional. &lt;BR&gt;&lt;B&gt;Recomendação de Limpeza:&lt;/B&gt; Utilize pano levemente úmido. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Observações importantes &lt;/B&gt;&lt;BR&gt;- Produto para uso residencial em ambiente interno, não devendo ficar exposto diretamente ao sol, calor e umidades excessivas.&lt;BR&gt;- Pode haver alguma diferença de tonalidade entre a imagem e o produto real, por conta do tratamento de imagens e a calibração de cores do seu monitor.&lt;BR&gt;- As imagens são meramente ilustrativas, não acompanham objetos de decoração e eletrônicos.&lt;BR&gt;- Ao receber a mercadoria, o cliente deve verificar as condições da embalagem, caso haja algum problema não assine o comprovante de recebimento.&lt;BR&gt;- Montagem, desmontagem e outras instalações serão de responsabilidade do cliente. Não nos responsabilizamos, no ato da entrega, por subir escadas/elevadores ou pelo transporte por guincho em apartamentos. Eventuais despesas são de responsabilidade do comprador.&lt;BR&gt;- Confira as dimensões do produto e certifique-se de que passará normalmente por supostos elevadores, portas, escadas e/ou corredores de sua residência.</t>
+          <t xml:space="preserve">&lt;B&gt;Guarda Roupa Casal 260cm Vidro Reflecta Vonn Nature/Fendi V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt; Desenvolvido para entregar glamour, requinte e sofisticação, eleva o padrão estético e funcional do quarto com presença marcante. O destaque do &lt;b&gt;Guarda Roupa&lt;/b&gt; fica por conta das portas com vidro reflecta, que proporcionam brilho, elegância e um toque contemporâneo ao &lt;b&gt;Quarto&lt;/b&gt;.&lt;br&gt;&lt;br&gt;
+A organização é favorecida pela divisão interna inteligente, pensada para acomodar roupas, acessórios e objetos pessoais com praticidade. Conta ainda com 6 portas com dobradiças com amortecimento, garantindo fechamento suave, silencioso e maior durabilidade no &lt;b&gt;Guarda Roupa&lt;/b&gt;.&lt;br&gt;&lt;br&gt;
+O &lt;b&gt;Guarda Roupa&lt;/b&gt; possui 4 gavetas com corrediças telescópicas, que oferecem abertura suave e excelente resistência no uso diário. A estrutura em MDF assegura robustez, estabilidade e qualidade superior ao móvel.&lt;br&gt;&lt;br&gt;
+Os puxadores em alumínio reforçam o acabamento premium e agregam ainda mais sofisticação ao design do seu &lt;b&gt;Quarto&lt;/b&gt;. Já os pés resistentes garantem firmeza, sustentação e segurança para o uso contínuo. &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;ESPECIFICAÇÕES&lt;/b&gt; &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;Dimensões do Produto &lt;/b&gt;&lt;br /&gt;                
+&lt;b&gt;Largura&lt;/b&gt;:        260 cm.        &lt;br /&gt;
+&lt;b&gt;Altura:&lt;/b&gt;        235 cm.        &lt;br /&gt;
+&lt;b&gt;Profundidade:&lt;/b&gt;        56 cm.        &lt;br /&gt;
+&lt;b&gt;Peso:&lt;/b&gt;        200 Kg.        &lt;br /&gt;
+&lt;br /&gt;                
+&lt;b&gt;Características do Produto &lt;/b&gt;&lt;br /&gt;                
+&lt;b&gt;Material da Estrutura:&lt;/b&gt;        MDF.        &lt;br /&gt;
+&lt;b&gt;Espessura das Chapas:&lt;/b&gt;        15mm.        &lt;br /&gt;
+&lt;b&gt;Peso suportado:&lt;/b&gt;        72 kg distribuídos.        &lt;br /&gt;
+&lt;b&gt;Acabamento:&lt;/b&gt;        Pintura UV.        &lt;br /&gt;
+&lt;b&gt;Escala de Brilho:&lt;/b&gt;        Fosco.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Portas:&lt;/b&gt;        6 portas.        &lt;br /&gt;
+&lt;b&gt;Tipo de Porta:&lt;/b&gt;        Convencional.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Cabideiro:&lt;/b&gt;        3 cabideiros.        &lt;br /&gt;
+&lt;b&gt;Material do Cabideiro:&lt;/b&gt;        Alumínio.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Gavetas:&lt;/b&gt;        4 gavetas.        &lt;br /&gt;
+&lt;b&gt;Tipo de Corrediças:&lt;/b&gt;        Telescópicas.        &lt;br /&gt;
+&lt;b&gt;Material do Puxador:&lt;/b&gt;        Alumínio.        &lt;br /&gt;
+&lt;b&gt;Quantidade de Prateleiras:&lt;/b&gt;        10 prateleiras.        &lt;br /&gt;
+&lt;b&gt;Material dos Pés:&lt;/b&gt;        PVC.        &lt;br /&gt;
+&lt;b&gt;Diferenciais: &lt;/b&gt;&lt;br /&gt;                
+- Design moderno.&lt;br /&gt;                
+- Portas de vidros reflecta.&lt;br /&gt;                
+- Corrediças telescópicas.&lt;br /&gt;                
+- Puxador em alumínio.&lt;br /&gt;                
+- Pés PVC.&lt;br /&gt;                
+- Cabideiros em alumínio.&lt;br /&gt;                
+&lt;b&gt;Sistema de Montagem:&lt;/b&gt;        Cavilhas / Parafusos.        &lt;br /&gt;
+&lt;b&gt;Manual de Montagem:&lt;/b&gt;        Sim.        &lt;br /&gt;
+&lt;b&gt;Complexidade da Montagem:&lt;/b&gt;        Alta.        &lt;br /&gt;
+&lt;b&gt;Volumes:&lt;/b&gt;        6 Volumes.        &lt;br /&gt;
+&lt;b&gt;Conteúdo da embalagem:&lt;/b&gt;        1 Guarda Roupa.        &lt;br /&gt;
+&lt;b&gt;Garantia do Fabricante:&lt;/b&gt;        90 dias contra defeito de fabricação.        &lt;br /&gt;
+&lt;b&gt;Montagem:&lt;/b&gt;        Recomendamos que seja feita por um profissional.        &lt;br /&gt;
+&lt;b&gt;Recomendação de Limpeza:&lt;/b&gt;        Utilize pano levemente úmido.        &lt;br /&gt;
+</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5295,30 +5706,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7901064702783</t>
+          <t>7901064725447</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>50019-107</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA BRANCO</t>
+          <t>MESA DE CABECEIRA DUBAI/LIOR NATURE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA</t>
+          <t>MESA DE CABECEIRA DUBAI/L</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA BRANCO</t>
+          <t>MESA DE CABECEIRA DUBAI/LIOR NATURE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA BRANCO</t>
+          <t>MESA DE CABECEIRA DUBAI/LIOR NATURE</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5328,16 +5744,18 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>GUARDA ROUPAS</t>
+          <t>CRIADO MUDO</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>GUARDA ROUPAS</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>73</v>
+          <t>MESA DE CABECEIRA</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Mesa de Cabeceira 50cm 2 Gavetas Lior Nature V02 - Mpozenato COD FAB: 50019-107 COR: NATURE</t>
+        </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -5355,22 +5773,32 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" t="n">
-        <v>64</v>
-      </c>
-      <c r="W11" t="n">
-        <v>63</v>
-      </c>
-      <c r="X11" t="n">
-        <v>35</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="AB11" t="n">
         <v>90</v>
@@ -5378,8 +5806,10 @@
       <c r="AC11" t="n">
         <v>1000</v>
       </c>
-      <c r="AD11" t="n">
-        <v>3</v>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -5423,7 +5853,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>Guarda Roupa Solteiro 154cm Com Espelho Mayra Branco Flex V02 - Mpozenato</t>
+          <t>Mesa de Cabeceira 50cm 2 Gavetas Lior Nature V02 - Mpozenato</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5436,12 +5866,44 @@
           <t>90 dias após o recebimento do produto</t>
         </is>
       </c>
-      <c r="AQ11" t="n">
-        <v>3</v>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;B&gt;Guarda Roupa Solteiro 154cm Com Espelho Mayra Branco Flex V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;O &lt;B&gt;Guarda Roupa Mayra&lt;/B&gt; é a solução compacta e funcional para quem busca otimizar o espaço sem abrir mão da organização. Com seis portas, sendo duas &lt;B&gt;Portas Com Espelho&lt;/B&gt;, e duas gavetas, ele oferece amplo espaço interno para organizar roupas, sapatos e outros pertences de maneira eficiente. Suas cincos prateleiras são perfeitas para manter tudo organizado, enquanto o espaço para cabides facilita o acesso rápido às suas peças favoritas. &lt;BR&gt;&lt;BR&gt;Este &lt;B&gt;Guarda Roupa&lt;/B&gt; foi projetado para oferecer praticidade no dia a dia. As gavetas são equipadas com corrediças metálicas, garantindo durabilidade e facilidade de uso, enquanto os puxadores oferecem uma pegada confortável e ergonômica. &lt;BR&gt;&lt;BR&gt;Os pés elevados do guarda roupa protegem o móvel da umidade, aumentando sua vida útil e garantindo uma melhor circulação de ar. Além disso, o design do guarda roupa com vistas flex é pensado para valorizar o ambiente e trazer uma sensação de aconchego e sofisticação ao seu quarto.&lt;BR&gt;&lt;BR&gt;Compacto e altamente funcional, é a escolha perfeita para quem busca praticidade, durabilidade e estilo. Seu design inteligente e detalhado proporciona uma excelente experiência no seu &lt;B&gt;Quarto Solteiro&lt;/B&gt;, mantendo tudo organizado e ao seu alcance com muito mais facilidade. &lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;ESPECIFICAÇÕES&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;Dimensões do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Largura&lt;/B&gt;: 154 cm. &lt;BR&gt;&lt;B&gt;Altura:&lt;/B&gt; 181 cm. &lt;BR&gt;&lt;B&gt;Profundidade:&lt;/B&gt; 40 cm. &lt;BR&gt;&lt;B&gt;Peso:&lt;/B&gt; 62,5Kg. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Características do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Material da Estrutura:&lt;/B&gt; MDP. &lt;BR&gt;&lt;B&gt;Espessura das Chapas:&lt;/B&gt; 12mm &lt;BR&gt;&lt;B&gt;Material do Fundo:&lt;/B&gt; MDF 3mm. &lt;BR&gt;&lt;B&gt;Peso Suportado:&lt;/B&gt; 61 kg distribuídos. &lt;BR&gt;&lt;B&gt;Acabamento:&lt;/B&gt; Pintura UV. &lt;BR&gt;&lt;B&gt;Escala de Brilho:&lt;/B&gt; Acetinado/Fosco. &lt;BR&gt;&lt;B&gt;Quantidade de Portas:&lt;/B&gt; 6 Portas. &lt;BR&gt;&lt;B&gt;Material da Dobradiça:&lt;/B&gt; Metal. &lt;BR&gt;&lt;B&gt;Tipo de Porta:&lt;/B&gt; Convencional. &lt;BR&gt;&lt;B&gt;Possui Cabideiros:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Cabideiro:&lt;/B&gt; 1 Cabideiro. &lt;BR&gt;&lt;B&gt;Material do Cabideiro:&lt;/B&gt; Madeira. &lt;BR&gt;&lt;B&gt;Possui Gaveta:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Gavetas:&lt;/B&gt; 2 Gavetas. &lt;BR&gt;&lt;B&gt;Tipo de Corrediças:&lt;/B&gt; Metálicas. &lt;BR&gt;&lt;B&gt;Material do Puxador:&lt;/B&gt; Plástico ABS. &lt;BR&gt;&lt;B&gt;Possui Prateleiras:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Prateleiras:&lt;/B&gt; 5 Prateleiras. &lt;BR&gt;&lt;B&gt;Possui Pés:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Pés:&lt;/B&gt; 4 Pés. &lt;BR&gt;&lt;B&gt;Material dos Pés: &lt;/B&gt;Plástico PVC. &lt;BR&gt;&lt;B&gt;Possui Espelho:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Diferenciais: &lt;/B&gt;&lt;BR&gt;- Prateleiras amplas.&lt;BR&gt;- Corrediças metálicas.&lt;BR&gt;- Desing moderno.&lt;BR&gt;- Vistas Flex.&lt;BR&gt;- Portas com dobradiças metálicas.&lt;BR&gt;- Portas com espelho.&lt;BR&gt;&lt;B&gt;Sistema de Montagem:&lt;/B&gt; Cavilhas/Parafusos. &lt;BR&gt;&lt;B&gt;Manual de Montagem:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Complexidade da Montagem:&lt;/B&gt; Média. &lt;BR&gt;&lt;B&gt;Volumes:&lt;/B&gt; 3 Volumes. &lt;BR&gt;&lt;B&gt;Conteúdo da embalagem:&lt;/B&gt; 1 Guarda Roupa. &lt;BR&gt;&lt;B&gt;Garantia do Fabricante:&lt;/B&gt; 90 dias contra defeito de fabricação. &lt;BR&gt;&lt;B&gt;Montagem:&lt;/B&gt; Recomendamos que seja feita por um profissional. &lt;BR&gt;&lt;B&gt;Recomendação de Limpeza:&lt;/B&gt; Utilize pano levemente úmido. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Observações importantes &lt;/B&gt;&lt;BR&gt;- Produto para uso residencial em ambiente interno, não devendo ficar exposto diretamente ao sol, calor e umidades excessivas.&lt;BR&gt;- Pode haver alguma diferença de tonalidade entre a imagem e o produto real, por conta do tratamento de imagens e a calibração de cores do seu monitor.&lt;BR&gt;- As imagens são meramente ilustrativas, não acompanham objetos de decoração e eletrônicos.&lt;BR&gt;- Ao receber a mercadoria, o cliente deve verificar as condições da embalagem, caso haja algum problema não assine o comprovante de recebimento.&lt;BR&gt;- Montagem, desmontagem e outras instalações serão de responsabilidade do cliente. Não nos responsabilizamos, no ato da entrega, por subir escadas/elevadores ou pelo transporte por guincho em apartamentos. Eventuais despesas são de responsabilidade do comprador.&lt;BR&gt;- Confira as dimensões do produto e certifique-se de que passará normalmente por supostos elevadores, portas, escadas e/ou corredores de sua residência.
+          <t xml:space="preserve">&lt;B&gt;Mesa de Cabeceira 50cm 2 Gavetas Lior Nature V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt; Ideal para complementar o quarto com praticidade, a &lt;b&gt;Mesa de Cabeceira&lt;/b&gt; oferece duas gavetas espaçosas que mantêm seus itens essenciais sempre organizados. Perfeita como mesa de apoio funcional, acomoda celular, luminária, livros e objetos decorativos com facilidade para o seu &lt;b&gt;Quarto&lt;/b&gt;.&lt;br&gt;&lt;br&gt;
+As gavetas da &lt;b&gt;Mesa de Cabeceira&lt;/b&gt; possuem corrediças telescópicas, garantindo abertura total e deslizamento suave no uso diário. Esse sistema assegura maior resistência e durabilidade, proporcionando conforto e eficiência ao abrir e fechar.&lt;br&gt;&lt;br&gt;
+Seu design une funcionalidade e elegância, contribuindo para um ambiente mais organizado e visualmente equilibrado. A estética versátil permite fácil combinação com diferentes estilos de decoração contemporânea.&lt;br&gt;&lt;br&gt;
+Compacta e prática, a &lt;b&gt;Mesa&lt;/b&gt; agrega presença discreta e sofisticada ao espaço sem sobrecarregar o &lt;b&gt;Quarto&lt;/b&gt;. Uma solução que entrega organização e estilo na medida certa para o dia a dia. &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;b&gt;ESPECIFICAÇÕES&lt;/b&gt; &lt;br /&gt;&lt;br /&gt;&lt;br /&gt; &lt;B&gt;Dimensões do Produto&lt;/B&gt;&lt;br&gt;                
+&lt;B&gt;Largura:&lt;/B&gt;        50 cm.        &lt;br&gt;
+&lt;B&gt;Altura:&lt;/B&gt;        58 cm.        &lt;br&gt;
+&lt;B&gt;Profundidade:&lt;/B&gt;        40 cm.        &lt;br&gt;
+&lt;B&gt;Peso:&lt;/B&gt;        15 Kg.        &lt;br&gt;
+&lt;br&gt;                
+&lt;B&gt;Características do Produto&lt;/B&gt;&lt;br&gt;                
+&lt;B&gt;Material da Estrutura:&lt;/B&gt;        MDP.        &lt;br&gt;
+&lt;b&gt;Espessura das Chapas:&lt;/b&gt;        15mm.        &lt;br /&gt;
+&lt;B&gt;Peso Suportado:&lt;/B&gt;        11 Kg distribuídos.        &lt;br&gt;
+&lt;B&gt;Acabamento:&lt;/B&gt;        Pintura UV.        &lt;br&gt;
+&lt;B&gt;Escala de Brilho:&lt;/B&gt;        Fosco.        &lt;br&gt;
+&lt;B&gt;Quantidade de Gavetas:&lt;/B&gt;        2 gavetas.        &lt;br&gt;
+&lt;B&gt;Tipo de Corrediças:&lt;/B&gt;        Telescópicas.        &lt;br&gt;
+&lt;B&gt;Tipo dos Puxadores:&lt;/B&gt;        ABS.        &lt;br&gt;
+&lt;B&gt;Diferenciais:&lt;/B&gt;&lt;br&gt;                
+- Design moderno.&lt;br /&gt;                
+- Gavetas com corrediças telescópicas.&lt;br /&gt;                
+- Puxador em ABS.&lt;br /&gt;                
+- Com sapatas plásticas.&lt;br /&gt;                
+&lt;B&gt;Sistema de Montagem:&lt;/B&gt;        Parafusos/Cavilhas/Minifix.        &lt;br&gt;
+&lt;B&gt;Manual de Montagem:&lt;/B&gt;        Sim.        &lt;br&gt;
+&lt;B&gt;Complexidade da Montagem:&lt;/B&gt;        Baixa.        &lt;br&gt;
+&lt;B&gt;Volumes:&lt;/B&gt;        1 Volume.        &lt;br&gt;
+&lt;B&gt;Conteúdo da Embalagem:&lt;/B&gt;        1 Mesa de Cabeceira.        &lt;br&gt;
+&lt;B&gt;Garantia do Fabricante:&lt;/B&gt;        90 dias contra defeito de fabricação.        &lt;br&gt;
+&lt;B&gt;Montagem:&lt;/B&gt;        Recomendamos que seja feita por um profissional.        &lt;br&gt;
+&lt;B&gt;Recomendação de Limpeza:&lt;/B&gt;        Utilize pano úmido.        &lt;br&gt;
 </t>
         </is>
       </c>
@@ -5451,840 +5913,6 @@
         </is>
       </c>
       <c r="AT11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>7901064702790</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA IMBUIA/CHP</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA IMBUIA/CHP</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA IMBUIA/CHP</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>VILA RICA</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>GUARDA ROUPAS</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>GUARDA ROUPAS</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>78</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>64</v>
-      </c>
-      <c r="W12" t="n">
-        <v>63</v>
-      </c>
-      <c r="X12" t="n">
-        <v>35</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>101</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>9403.50.00</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>NAO</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>Guarda Roupa Solteiro 154cm Com Espelho Mayra Imbuia/Champanhe V02 - Mpozenato</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Mpozenato</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>90 dias após o recebimento do produto</t>
-        </is>
-      </c>
-      <c r="AQ12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;B&gt;Guarda Roupa Solteiro 154cm Com Espelho Mayra Imbuia/Champanhe V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;O &lt;B&gt;Guarda Roupa Mayra&lt;/B&gt; é a solução compacta e funcional para quem busca otimizar o espaço sem abrir mão da organização. Com seis portas, sendo duas &lt;B&gt;Portas Com Espelho&lt;/B&gt;, e duas gavetas, ele oferece amplo espaço interno para organizar roupas, sapatos e outros pertences de maneira eficiente. Suas cincos prateleiras são perfeitas para manter tudo organizado, enquanto o espaço para cabides facilita o acesso rápido às suas peças favoritas. &lt;BR&gt;&lt;BR&gt;Este &lt;B&gt;Guarda Roupa&lt;/B&gt; foi projetado para oferecer praticidade no dia a dia. As gavetas são equipadas com corrediças metálicas, garantindo durabilidade e facilidade de uso, enquanto os puxadores oferecem uma pegada confortável e ergonômica. &lt;BR&gt;&lt;BR&gt;Os pés elevados do guarda roupa protegem o móvel da umidade, aumentando sua vida útil e garantindo uma melhor circulação de ar. Além disso, o design do guarda roupa é pensado para valorizar o ambiente e trazer uma sensação de aconchego e sofisticação ao seu quarto. &lt;BR&gt;&lt;BR&gt;Compacto e altamente funcional, é a escolha perfeita para quem busca praticidade, durabilidade e estilo. Seu design inteligente e detalhado proporciona uma excelente experiência no seu &lt;B&gt;Quarto Solteiro&lt;/B&gt;, mantendo tudo organizado e ao seu alcance com muito mais facilidade. &lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;ESPECIFICAÇÕES&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;Dimensões do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Largura&lt;/B&gt;: 154 cm. &lt;BR&gt;&lt;B&gt;Altura:&lt;/B&gt; 181 cm. &lt;BR&gt;&lt;B&gt;Profundidade:&lt;/B&gt; 40 cm. &lt;BR&gt;&lt;B&gt;Peso:&lt;/B&gt; 62,5Kg. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Características do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Material da Estrutura:&lt;/B&gt; MDP. &lt;BR&gt;&lt;B&gt;Espessura das Chapas:&lt;/B&gt; 12mm &lt;BR&gt;&lt;B&gt;Material do Fundo:&lt;/B&gt; MDF 3mm. &lt;BR&gt;&lt;B&gt;Peso Suportado:&lt;/B&gt; 61 kg distribuídos. &lt;BR&gt;&lt;B&gt;Acabamento:&lt;/B&gt; Pintura UV. &lt;BR&gt;&lt;B&gt;Escala de Brilho:&lt;/B&gt; Acetinado/Fosco. &lt;BR&gt;&lt;B&gt;Quantidade de Portas:&lt;/B&gt; 6 Portas. &lt;BR&gt;&lt;B&gt;Material da Dobradiça:&lt;/B&gt; Metal. &lt;BR&gt;&lt;B&gt;Tipo de Porta:&lt;/B&gt; Convencional. &lt;BR&gt;&lt;B&gt;Possui Cabideiros:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Cabideiro:&lt;/B&gt; 1 Cabideiro. &lt;BR&gt;&lt;B&gt;Material do Cabideiro:&lt;/B&gt; Madeira. &lt;BR&gt;&lt;B&gt;Possui Gaveta:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Gavetas:&lt;/B&gt; 2 Gavetas. &lt;BR&gt;&lt;B&gt;Tipo de Corrediças:&lt;/B&gt; Metálicas. &lt;BR&gt;&lt;B&gt;Material do Puxador:&lt;/B&gt; Plástico ABS. &lt;BR&gt;&lt;B&gt;Possui Prateleiras:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Prateleiras:&lt;/B&gt; 5 Prateleiras. &lt;BR&gt;&lt;B&gt;Possui Pés:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Pés:&lt;/B&gt; 4 Pés. &lt;BR&gt;&lt;B&gt;Material dos Pés: &lt;/B&gt;Plástico PVC. &lt;BR&gt;&lt;B&gt;Possui Espelho:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Diferenciais: &lt;/B&gt;&lt;BR&gt;- Prateleiras amplas.&lt;BR&gt;- Corrediças metálicas.&lt;BR&gt;- Desing moderno.&lt;BR&gt;- Portas com dobradiças metálicas.&lt;BR&gt;- Portas com espelho.&lt;BR&gt;&lt;B&gt;Sistema de Montagem:&lt;/B&gt; Cavilhas/Parafusos. &lt;BR&gt;&lt;B&gt;Manual de Montagem:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Complexidade da Montagem:&lt;/B&gt; Média. &lt;BR&gt;&lt;B&gt;Volumes:&lt;/B&gt; 3 Volumes. &lt;BR&gt;&lt;B&gt;Conteúdo da embalagem:&lt;/B&gt; 1 Guarda Roupa. &lt;BR&gt;&lt;B&gt;Garantia do Fabricante:&lt;/B&gt; 90 dias contra defeito de fabricação. &lt;BR&gt;&lt;B&gt;Montagem:&lt;/B&gt; Recomendamos que seja feita por um profissional. &lt;BR&gt;&lt;B&gt;Recomendação de Limpeza:&lt;/B&gt; Utilize pano levemente úmido. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Observações importantes &lt;/B&gt;&lt;BR&gt;- Produto para uso residencial em ambiente interno, não devendo ficar exposto diretamente ao sol, calor e umidades excessivas.&lt;BR&gt;- Pode haver alguma diferença de tonalidade entre a imagem e o produto real, por conta do tratamento de imagens e a calibração de cores do seu monitor.&lt;BR&gt;- As imagens são meramente ilustrativas, não acompanham objetos de decoração e eletrônicos.&lt;BR&gt;- Ao receber a mercadoria, o cliente deve verificar as condições da embalagem, caso haja algum problema não assine o comprovante de recebimento.&lt;BR&gt;- Montagem, desmontagem e outras instalações serão de responsabilidade do cliente. Não nos responsabilizamos, no ato da entrega, por subir escadas/elevadores ou pelo transporte por guincho em apartamentos. Eventuais despesas são de responsabilidade do comprador.&lt;BR&gt;- Confira as dimensões do produto e certifique-se de que passará normalmente por supostos elevadores, portas, escadas e/ou corredores de sua residência.
-</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>7901064702806</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA IMBUIA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA IMBUIA</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA IMBUIA</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>VILA RICA</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>GUARDA ROUPAS</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>GUARDA ROUPAS</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" t="n">
-        <v>64</v>
-      </c>
-      <c r="W13" t="n">
-        <v>63</v>
-      </c>
-      <c r="X13" t="n">
-        <v>35</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>101</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>9403.50.00</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>NAO</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>Guarda Roupa Solteiro 154cm Com Espelho Mayra Imbuia V02 - Mpozenato</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Mpozenato</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>90 dias após o recebimento do produto</t>
-        </is>
-      </c>
-      <c r="AQ13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;B&gt;Guarda Roupa Solteiro 154cm Com Espelho Mayra Imbuia V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;O &lt;B&gt;Guarda Roupa Mayra&lt;/B&gt; é a solução compacta e funcional para quem busca otimizar o espaço sem abrir mão da organização. Com seis portas, sendo duas &lt;B&gt;Portas Com Espelho&lt;/B&gt;, e duas gavetas, ele oferece amplo espaço interno para organizar roupas, sapatos e outros pertences de maneira eficiente. Suas cincos prateleiras são perfeitas para manter tudo organizado, enquanto o espaço para cabides facilita o acesso rápido às suas peças favoritas. &lt;BR&gt;&lt;BR&gt;Este &lt;B&gt;Guarda Roupa&lt;/B&gt; foi projetado para oferecer praticidade no dia a dia. As gavetas são equipadas com corrediças metálicas, garantindo durabilidade e facilidade de uso, enquanto os puxadores oferecem uma pegada confortável e ergonômica. &lt;BR&gt;&lt;BR&gt;Os pés elevados do guarda roupa protegem o móvel da umidade, aumentando sua vida útil e garantindo uma melhor circulação de ar. Além disso, o design do guarda roupa é pensado para valorizar o ambiente e trazer uma sensação de aconchego e sofisticação ao seu quarto. &lt;BR&gt;&lt;BR&gt;Compacto e altamente funcional, é a escolha perfeita para quem busca praticidade, durabilidade e estilo. Seu design inteligente e detalhado proporciona uma excelente experiência no seu &lt;B&gt;Quarto Solteiro&lt;/B&gt;, mantendo tudo organizado e ao seu alcance com muito mais facilidade. &lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;ESPECIFICAÇÕES&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;Dimensões do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Largura&lt;/B&gt;: 154 cm. &lt;BR&gt;&lt;B&gt;Altura:&lt;/B&gt; 181 cm. &lt;BR&gt;&lt;B&gt;Profundidade:&lt;/B&gt; 40 cm. &lt;BR&gt;&lt;B&gt;Peso:&lt;/B&gt; 62,5Kg. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Características do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Material da Estrutura:&lt;/B&gt; MDP. &lt;BR&gt;&lt;B&gt;Espessura das Chapas:&lt;/B&gt; 12mm &lt;BR&gt;&lt;B&gt;Material do Fundo:&lt;/B&gt; MDF 3mm. &lt;BR&gt;&lt;B&gt;Peso Suportado:&lt;/B&gt; 61 kg distribuídos. &lt;BR&gt;&lt;B&gt;Acabamento:&lt;/B&gt; Pintura UV. &lt;BR&gt;&lt;B&gt;Escala de Brilho:&lt;/B&gt; Acetinado/Fosco. &lt;BR&gt;&lt;B&gt;Quantidade de Portas:&lt;/B&gt; 6 Portas. &lt;BR&gt;&lt;B&gt;Material da Dobradiça:&lt;/B&gt; Metal. &lt;BR&gt;&lt;B&gt;Tipo de Porta:&lt;/B&gt; Convencional. &lt;BR&gt;&lt;B&gt;Possui Cabideiros:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Cabideiro:&lt;/B&gt; 1 Cabideiro. &lt;BR&gt;&lt;B&gt;Material do Cabideiro:&lt;/B&gt; Madeira. &lt;BR&gt;&lt;B&gt;Possui Gaveta:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Gavetas:&lt;/B&gt; 2 Gavetas. &lt;BR&gt;&lt;B&gt;Tipo de Corrediças:&lt;/B&gt; Metálicas. &lt;BR&gt;&lt;B&gt;Material do Puxador:&lt;/B&gt; Plástico ABS. &lt;BR&gt;&lt;B&gt;Possui Prateleiras:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Prateleiras:&lt;/B&gt; 5 Prateleiras. &lt;BR&gt;&lt;B&gt;Possui Pés:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Pés:&lt;/B&gt; 4 Pés. &lt;BR&gt;&lt;B&gt;Material dos Pés: &lt;/B&gt;Plástico PVC. &lt;BR&gt;&lt;B&gt;Possui Espelho:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Diferenciais: &lt;/B&gt;&lt;BR&gt;- Prateleiras amplas.&lt;BR&gt;- Corrediças metálicas.&lt;BR&gt;- Desing moderno.&lt;BR&gt;- Portas com dobradiças metálicas.&lt;BR&gt;- Portas com espelho.&lt;BR&gt;&lt;B&gt;Sistema de Montagem:&lt;/B&gt; Cavilhas/Parafusos. &lt;BR&gt;&lt;B&gt;Manual de Montagem:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Complexidade da Montagem:&lt;/B&gt; Média. &lt;BR&gt;&lt;B&gt;Volumes:&lt;/B&gt; 3 Volumes. &lt;BR&gt;&lt;B&gt;Conteúdo da embalagem:&lt;/B&gt; 1 Guarda Roupa. &lt;BR&gt;&lt;B&gt;Garantia do Fabricante:&lt;/B&gt; 90 dias contra defeito de fabricação. &lt;BR&gt;&lt;B&gt;Montagem:&lt;/B&gt; Recomendamos que seja feita por um profissional. &lt;BR&gt;&lt;B&gt;Recomendação de Limpeza:&lt;/B&gt; Utilize pano levemente úmido. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Observações importantes &lt;/B&gt;&lt;BR&gt;- Produto para uso residencial em ambiente interno, não devendo ficar exposto diretamente ao sol, calor e umidades excessivas.&lt;BR&gt;- Pode haver alguma diferença de tonalidade entre a imagem e o produto real, por conta do tratamento de imagens e a calibração de cores do seu monitor.&lt;BR&gt;- As imagens são meramente ilustrativas, não acompanham objetos de decoração e eletrônicos.&lt;BR&gt;- Ao receber a mercadoria, o cliente deve verificar as condições da embalagem, caso haja algum problema não assine o comprovante de recebimento.&lt;BR&gt;- Montagem, desmontagem e outras instalações serão de responsabilidade do cliente. Não nos responsabilizamos, no ato da entrega, por subir escadas/elevadores ou pelo transporte por guincho em apartamentos. Eventuais despesas são de responsabilidade do comprador.&lt;BR&gt;- Confira as dimensões do produto e certifique-se de que passará normalmente por supostos elevadores, portas, escadas e/ou corredores de sua residência.
-</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>7901064702813</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA NT/CHP/BRISA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA NT/CHP/BRISA</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA NT/CHP/BRISA</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>VILA RICA</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>GUARDA ROUPAS</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>GUARDA ROUPAS</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>78</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>64</v>
-      </c>
-      <c r="W14" t="n">
-        <v>63</v>
-      </c>
-      <c r="X14" t="n">
-        <v>35</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>101</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>9403.50.00</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>NAO</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>Guarda Roupa Solteiro 154cm Com Espelho Mayra Nature/Champanhe V02 - Mpozenato</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Mpozenato</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>90 dias após o recebimento do produto</t>
-        </is>
-      </c>
-      <c r="AQ14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;B&gt;Guarda Roupa Solteiro 154cm Com Espelho Mayra Nature/Champanhe V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;O &lt;B&gt;Guarda Roupa Mayra&lt;/B&gt; é a solução compacta e funcional para quem busca otimizar o espaço sem abrir mão da organização. Com seis portas, sendo duas &lt;B&gt;Portas Com Espelho&lt;/B&gt;, e duas gavetas, ele oferece amplo espaço interno para organizar roupas, sapatos e outros pertences de maneira eficiente. Suas cincos prateleiras são perfeitas para manter tudo organizado, enquanto o espaço para cabides facilita o acesso rápido às suas peças favoritas. &lt;BR&gt;&lt;BR&gt;Este &lt;B&gt;Guarda Roupa&lt;/B&gt; foi projetado para oferecer praticidade no dia a dia. As gavetas são equipadas com corrediças metálicas, garantindo durabilidade e facilidade de uso, enquanto os puxadores oferecem uma pegada confortável e ergonômica. &lt;BR&gt;&lt;BR&gt;Os pés elevados do guarda roupa protegem o móvel da umidade, aumentando sua vida útil e garantindo uma melhor circulação de ar. Além disso, o design do guarda roupa é pensado para valorizar o ambiente e trazer uma sensação de aconchego e sofisticação ao seu quarto. &lt;BR&gt;&lt;BR&gt;Compacto e altamente funcional, é a escolha perfeita para quem busca praticidade, durabilidade e estilo. Seu design inteligente e detalhado proporciona uma excelente experiência no seu &lt;B&gt;Quarto Solteiro&lt;/B&gt;, mantendo tudo organizado e ao seu alcance com muito mais facilidade. &lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;ESPECIFICAÇÕES&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;Dimensões do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Largura&lt;/B&gt;: 154 cm. &lt;BR&gt;&lt;B&gt;Altura:&lt;/B&gt; 181 cm. &lt;BR&gt;&lt;B&gt;Profundidade:&lt;/B&gt; 40 cm. &lt;BR&gt;&lt;B&gt;Peso:&lt;/B&gt; 62,5Kg. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Características do Produto &lt;/B&gt;&lt;BR&gt;&lt;B&gt;Material da Estrutura:&lt;/B&gt; MDP. &lt;BR&gt;&lt;B&gt;Espessura das Chapas:&lt;/B&gt; 12mm &lt;BR&gt;&lt;B&gt;Material do Fundo:&lt;/B&gt; MDF 3mm. &lt;BR&gt;&lt;B&gt;Peso Suportado:&lt;/B&gt; 61 kg distribuídos. &lt;BR&gt;&lt;B&gt;Acabamento:&lt;/B&gt; Pintura UV. &lt;BR&gt;&lt;B&gt;Escala de Brilho:&lt;/B&gt; Acetinado/Fosco. &lt;BR&gt;&lt;B&gt;Quantidade de Portas:&lt;/B&gt; 6 Portas. &lt;BR&gt;&lt;B&gt;Material da Dobradiça:&lt;/B&gt; Metal. &lt;BR&gt;&lt;B&gt;Tipo de Porta:&lt;/B&gt; Convencional. &lt;BR&gt;&lt;B&gt;Possui Cabideiros:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Cabideiro:&lt;/B&gt; 1 Cabideiro. &lt;BR&gt;&lt;B&gt;Material do Cabideiro:&lt;/B&gt; Madeira. &lt;BR&gt;&lt;B&gt;Possui Gaveta:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Gavetas:&lt;/B&gt; 2 Gavetas. &lt;BR&gt;&lt;B&gt;Tipo de Corrediças:&lt;/B&gt; Metálicas. &lt;BR&gt;&lt;B&gt;Material do Puxador:&lt;/B&gt; Plástico ABS. &lt;BR&gt;&lt;B&gt;Possui Prateleiras:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Prateleiras:&lt;/B&gt; 5 Prateleiras. &lt;BR&gt;&lt;B&gt;Possui Pés:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Quantidade de Pés:&lt;/B&gt; 4 Pés. &lt;BR&gt;&lt;B&gt;Material dos Pés: &lt;/B&gt;Plástico PVC. &lt;BR&gt;&lt;B&gt;Possui Espelho:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Diferenciais: &lt;/B&gt;&lt;BR&gt;- Prateleiras amplas.&lt;BR&gt;- Corrediças metálicas.&lt;BR&gt;- Desing moderno.&lt;BR&gt;- Portas com dobradiças metálicas.&lt;BR&gt;- Portas com espelho.&lt;BR&gt;&lt;B&gt;Sistema de Montagem:&lt;/B&gt; Cavilhas/Parafusos. &lt;BR&gt;&lt;B&gt;Manual de Montagem:&lt;/B&gt; Sim. &lt;BR&gt;&lt;B&gt;Complexidade da Montagem:&lt;/B&gt; Média. &lt;BR&gt;&lt;B&gt;Volumes:&lt;/B&gt; 3 Volumes. &lt;BR&gt;&lt;B&gt;Conteúdo da embalagem:&lt;/B&gt; 1 Guarda Roupa. &lt;BR&gt;&lt;B&gt;Garantia do Fabricante:&lt;/B&gt; 90 dias contra defeito de fabricação. &lt;BR&gt;&lt;B&gt;Montagem:&lt;/B&gt; Recomendamos que seja feita por um profissional. &lt;BR&gt;&lt;B&gt;Recomendação de Limpeza:&lt;/B&gt; Utilize pano levemente úmido. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Observações importantes &lt;/B&gt;&lt;BR&gt;- Produto para uso residencial em ambiente interno, não devendo ficar exposto diretamente ao sol, calor e umidades excessivas.&lt;BR&gt;- Pode haver alguma diferença de tonalidade entre a imagem e o produto real, por conta do tratamento de imagens e a calibração de cores do seu monitor.&lt;BR&gt;- As imagens são meramente ilustrativas, não acompanham objetos de decoração e eletrônicos.&lt;BR&gt;- Ao receber a mercadoria, o cliente deve verificar as condições da embalagem, caso haja algum problema não assine o comprovante de recebimento.&lt;BR&gt;- Montagem, desmontagem e outras instalações serão de responsabilidade do cliente. Não nos responsabilizamos, no ato da entrega, por subir escadas/elevadores ou pelo transporte por guincho em apartamentos. Eventuais despesas são de responsabilidade do comprador.&lt;BR&gt;- Confira as dimensões do produto e certifique-se de que passará normalmente por supostos elevadores, portas, escadas e/ou corredores de sua residência.
-</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>7901064702820</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>20019-91</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>COMODA SIRIUS/LIRIO IMBUIA/CHP</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>COMODA SIRIUS/LIRIO IMBUI</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>COMODA SIRIUS/LIRIO IMBUIA/CHP</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>COMODA SIRIUS/LIRIO IMBUIA/CHP</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>VILA RICA</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>QUARTO ADULTO</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>CÔMODAS</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>44</v>
-      </c>
-      <c r="W15" t="n">
-        <v>43</v>
-      </c>
-      <c r="X15" t="n">
-        <v>48</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>129</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>9403.50.00</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>NAO</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>Cômoda Quarto Sapateira 2 Portas 4 Gavetas Lírio Imbuia/Champanhe V02 - Mpozenato</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Mpozenato</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>90 dias após o recebimento do produto</t>
-        </is>
-      </c>
-      <c r="AQ15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>&lt;B&gt;Cômoda Quarto Sapateira 2 Portas 4 Gavetas Lírio Imbuia/Champanhe V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;Se existe um móvel versátil, é a &lt;b&gt;Cômoda&lt;/b&gt;. Ela organiza roupas, objetos pessoais e até itens decorativos de forma prática. &lt;br&gt;&lt;br&gt;
-O modelo conta com duas portas, cinco gavetas amplas e prateleira interna que facilita a organização no &lt;b&gt;Quarto Casal Moderno&lt;/b&gt; ou &lt;b&gt;Quarto Planejado&lt;/b&gt;. &lt;br&gt;&lt;br&gt;
-Com design moderno, essa &lt;b&gt;Cômoda com Gavetas&lt;/b&gt; é funcional e elegante, combinando com diferentes estilos e necessidades do ambiente. &lt;br&gt;&lt;br&gt;
-Os pés em madeira elevam o móvel, protegendo contra umidade e contribuindo para maior resistência e durabilidade.&lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;ESPECIFICAÇÕES&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;Dimensões dos Produtos&lt;/B&gt;&lt;BR&gt;&lt;B&gt;Largura: &lt;/B&gt;122 cm. &lt;BR&gt;&lt;B&gt;Altura: &lt;/B&gt;96,5 cm. &lt;BR&gt;&lt;B&gt;Profundidade: &lt;/B&gt;47 cm. &lt;BR&gt;&lt;B&gt;Peso: &lt;/B&gt;43 Kg. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Características do Produto&lt;/B&gt;&lt;BR&gt;&lt;B&gt;Material da estrutura: &lt;/B&gt;MDP 12mm/15mm. &lt;BR&gt;&lt;B&gt;Acabamento: &lt;/B&gt;Pintura UV. &lt;BR&gt;&lt;B&gt;Escala de Brilho: &lt;/B&gt;Fosco. &lt;BR&gt;&lt;B&gt;Peso Suportado: &lt;/B&gt;5 kg por prateleira, 3 kg por gaveta. &lt;BR&gt;&lt;B&gt;Quantidade de Portas: &lt;/B&gt;2 Portas. &lt;BR&gt;&lt;B&gt;Tipo de Porta: &lt;/B&gt;Convencional. &lt;BR&gt;&lt;B&gt;Material dos Puxadores: &lt;/B&gt;MDF. &lt;BR&gt;&lt;B&gt;Quantidade de Gavetas: &lt;/B&gt;5 Gavetas. &lt;BR&gt;&lt;B&gt;Tipo de Corrediças: &lt;/B&gt;Metálicas. &lt;BR&gt;&lt;B&gt;Quantidade de Prateleiras: &lt;/B&gt;1 Prateleira. &lt;BR&gt;&lt;B&gt;Possui Cabideiro: &lt;/B&gt;Não. &lt;BR&gt;&lt;B&gt;Possui Pés: &lt;/B&gt;Sim. &lt;BR&gt;&lt;B&gt;Tipo de Pés: &lt;/B&gt;Pés Madeira/Sapatas Plásticas. &lt;BR&gt;&lt;B&gt;Diferenciais: &lt;/B&gt;&lt;BR&gt;- Design clássico. &lt;BR&gt;- Fundo em MDF 3mm. &lt;BR&gt;- Contém prateleira móvel. &lt;BR&gt;- Pode-se optar pela instalação dos pés ou das sapatas. &lt;BR&gt;&lt;B&gt;Sistema de Montagem: &lt;/B&gt;Parafusos/Cavilhas/Cantoneira. &lt;BR&gt;&lt;B&gt;Manual de Montagem: &lt;/B&gt;Sim. &lt;BR&gt;&lt;B&gt;Complexidade da Montagem: &lt;/B&gt;Média. &lt;BR&gt;&lt;B&gt;Volumes: &lt;/B&gt;1 Volume. &lt;BR&gt;&lt;B&gt;Conteúdo da Embalagem: &lt;/B&gt;1 Cômoda. &lt;BR&gt;&lt;B&gt;Garantia do Fabricante: &lt;/B&gt;90 dias contra defeito de fabricação. &lt;BR&gt;&lt;B&gt;Montagem: &lt;/B&gt;Recomendamos que seja feita por um profissional. &lt;BR&gt;&lt;B&gt;Recomendação de Limpeza: &lt;/B&gt;Utilize pano levemente úmido. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Observações importantes&lt;/B&gt;&lt;BR&gt;- Produto para uso residencial em ambiente interno, não devendo ficar exposto diretamente ao sol, calor e umidades excessivas. &lt;BR&gt;- Pode haver alguma diferença de tonalidade entre a imagem e o produto real, por conta do tratamento de imagens e a calibração de cores do seu monitor. &lt;BR&gt;- As imagens são meramente ilustrativas, não acompanham objetos de decoração e eletrônicos. &lt;BR&gt;- Confira o estado da embalagem, não devendo assinar o comprovante em caso de danos. &lt;BR&gt;- Não asseguramos, no ato da entrega, por subir escadas/elevadores, pelo transporte por guincho em apartamentos ou montagem, desmontagem e instalações. Eventuais despesas são por conta do comprador. &lt;BR&gt;- Confira as dimensões do produto e certifique-se de que passará normalmente por supostos elevadores, portas, escadas e/ou corredores de sua residência. &lt;BR&gt;</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>7901064702837</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>20019-80</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>COMODA SIRIUS/LIRIO IMBUIA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>COMODA SIRIUS/LIRIO IMBUI</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>COMODA SIRIUS/LIRIO IMBUIA</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>COMODA SIRIUS/LIRIO IMBUIA</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>VILA RICA</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>QUARTO ADULTO</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>CÔMODAS</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>71</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>44</v>
-      </c>
-      <c r="W16" t="n">
-        <v>43</v>
-      </c>
-      <c r="X16" t="n">
-        <v>48</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>129</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>9403.50.00</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>NAO</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>Cômoda Quarto Sapateira 2 Portas 4 Gavetas Lírio Imbuia V02 - Mpozenato</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Mpozenato</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>90 dias após o recebimento do produto</t>
-        </is>
-      </c>
-      <c r="AQ16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>&lt;B&gt;Cômoda Quarto Sapateira 2 Portas 4 Gavetas Lírio Imbuia V02 - Mpozenato&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;Se existe um móvel versátil, é a &lt;b&gt;Cômoda&lt;/b&gt;. Ela organiza roupas, objetos pessoais e até itens decorativos de forma prática. &lt;br&gt;&lt;br&gt;
-O modelo conta com duas portas, cinco gavetas amplas e prateleira interna que facilita a organização no &lt;b&gt;Quarto Casal Moderno&lt;/b&gt; ou &lt;b&gt;Quarto Planejado&lt;/b&gt;. &lt;br&gt;&lt;br&gt;
-Com design moderno, essa &lt;b&gt;Cômoda com Gavetas&lt;/b&gt; é funcional e elegante, combinando com diferentes estilos e necessidades do ambiente. &lt;br&gt;&lt;br&gt;
-Os pés em madeira elevam o móvel, protegendo contra umidade e contribuindo para maior resistência e durabilidade.&lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;ESPECIFICAÇÕES&lt;/B&gt;&lt;BR&gt;&lt;BR&gt;&lt;BR&gt;&lt;B&gt;Dimensões dos Produtos&lt;/B&gt;&lt;BR&gt;&lt;B&gt;Largura: &lt;/B&gt;122 cm. &lt;BR&gt;&lt;B&gt;Altura: &lt;/B&gt;96,5 cm. &lt;BR&gt;&lt;B&gt;Profundidade: &lt;/B&gt;47 cm. &lt;BR&gt;&lt;B&gt;Peso: &lt;/B&gt;43 Kg. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Características do Produto&lt;/B&gt;&lt;BR&gt;&lt;B&gt;Material da estrutura: &lt;/B&gt;MDP 12mm/15mm. &lt;BR&gt;&lt;B&gt;Acabamento: &lt;/B&gt;Pintura UV. &lt;BR&gt;&lt;B&gt;Escala de Brilho: &lt;/B&gt;Fosco. &lt;BR&gt;&lt;B&gt;Peso Suportado: &lt;/B&gt;5 kg por prateleira, 3 kg por gaveta. &lt;BR&gt;&lt;B&gt;Quantidade de Portas: &lt;/B&gt;2 Portas. &lt;BR&gt;&lt;B&gt;Tipo de Porta: &lt;/B&gt;Convencional. &lt;BR&gt;&lt;B&gt;Material dos Puxadores: &lt;/B&gt;MDF. &lt;BR&gt;&lt;B&gt;Quantidade de Gavetas: &lt;/B&gt;5 Gavetas. &lt;BR&gt;&lt;B&gt;Tipo de Corrediças: &lt;/B&gt;Metálicas. &lt;BR&gt;&lt;B&gt;Quantidade de Prateleiras: &lt;/B&gt;1 Prateleira. &lt;BR&gt;&lt;B&gt;Possui Cabideiro: &lt;/B&gt;Não. &lt;BR&gt;&lt;B&gt;Possui Pés: &lt;/B&gt;Sim. &lt;BR&gt;&lt;B&gt;Tipo de Pés: &lt;/B&gt;Pés Madeira/Sapatas Plásticas. &lt;BR&gt;&lt;B&gt;Diferenciais: &lt;/B&gt;&lt;BR&gt;- Design clássico. &lt;BR&gt;- Fundo em MDF 3mm. &lt;BR&gt;- Contém prateleira móvel. &lt;BR&gt;- Pode-se optar pela instalação dos pés ou das sapatas. &lt;BR&gt;&lt;B&gt;Sistema de Montagem: &lt;/B&gt;Parafusos/Cavilhas/Cantoneira. &lt;BR&gt;&lt;B&gt;Manual de Montagem: &lt;/B&gt;Sim. &lt;BR&gt;&lt;B&gt;Complexidade da Montagem: &lt;/B&gt;Média. &lt;BR&gt;&lt;B&gt;Volumes: &lt;/B&gt;1 Volume. &lt;BR&gt;&lt;B&gt;Conteúdo da Embalagem: &lt;/B&gt;1 Cômoda. &lt;BR&gt;&lt;B&gt;Garantia do Fabricante: &lt;/B&gt;90 dias contra defeito de fabricação. &lt;BR&gt;&lt;B&gt;Montagem: &lt;/B&gt;Recomendamos que seja feita por um profissional. &lt;BR&gt;&lt;B&gt;Recomendação de Limpeza: &lt;/B&gt;Utilize pano levemente úmido. &lt;BR&gt;&lt;BR&gt;&lt;B&gt;Observações importantes&lt;/B&gt;&lt;BR&gt;- Produto para uso residencial em ambiente interno, não devendo ficar exposto diretamente ao sol, calor e umidades excessivas. &lt;BR&gt;- Pode haver alguma diferença de tonalidade entre a imagem e o produto real, por conta do tratamento de imagens e a calibração de cores do seu monitor. &lt;BR&gt;- As imagens são meramente ilustrativas, não acompanham objetos de decoração e eletrônicos. &lt;BR&gt;- Confira o estado da embalagem, não devendo assinar o comprovante em caso de danos. &lt;BR&gt;- Não asseguramos, no ato da entrega, por subir escadas/elevadores, pelo transporte por guincho em apartamentos ou montagem, desmontagem e instalações. Eventuais despesas são por conta do comprador. &lt;BR&gt;- Confira as dimensões do produto e certifique-se de que passará normalmente por supostos elevadores, portas, escadas e/ou corredores de sua residência. &lt;BR&gt;</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -6307,7 +5935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col width="23.140625" customWidth="1" style="16" min="1" max="1"/>
@@ -6401,38 +6029,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7901064702707</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>229</v>
-      </c>
-      <c r="C2" t="n">
-        <v>190</v>
-      </c>
-      <c r="D2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>199.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>610.47</v>
-      </c>
-      <c r="I2" t="n">
-        <v>384.9</v>
-      </c>
-      <c r="J2" t="n">
-        <v>384.9</v>
+          <t>7901064725362</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>430.00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>21.50</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>451.50</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1381.59</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>897.90</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>897.90</t>
+        </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19/08/2055</t>
+          <t>04/03/2056</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -6444,38 +6091,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7901064702714</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>229</v>
-      </c>
-      <c r="C3" t="n">
-        <v>190</v>
-      </c>
-      <c r="D3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>199.5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>610.47</v>
-      </c>
-      <c r="I3" t="n">
-        <v>384.9</v>
-      </c>
-      <c r="J3" t="n">
-        <v>384.9</v>
+          <t>7901064725379</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>430.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>21.50</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>451.50</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1381.59</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>897.90</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>897.90</t>
+        </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19/08/2055</t>
+          <t>04/03/2056</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -6487,38 +6153,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7901064702721</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>229</v>
-      </c>
-      <c r="C4" t="n">
-        <v>255</v>
-      </c>
-      <c r="D4" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="G4" t="n">
-        <v>267.75</v>
-      </c>
-      <c r="H4" t="n">
-        <v>819.3200000000001</v>
-      </c>
-      <c r="I4" t="n">
-        <v>515.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>515.9</v>
+          <t>7901064725386</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>430.00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>21.50</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>451.50</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1381.59</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>897.90</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>897.90</t>
+        </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19/08/2055</t>
+          <t>04/03/2056</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -6530,38 +6215,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7901064702738</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>229</v>
-      </c>
-      <c r="C5" t="n">
-        <v>270</v>
-      </c>
-      <c r="D5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>283.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>867.51</v>
-      </c>
-      <c r="I5" t="n">
-        <v>546.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>546.9</v>
+          <t>7901064725393</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>430.00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>21.50</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>451.50</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1381.59</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>897.90</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>897.90</t>
+        </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>19/08/2055</t>
+          <t>04/03/2056</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -6573,38 +6277,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7901064702745</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>229</v>
-      </c>
-      <c r="C6" t="n">
-        <v>345</v>
-      </c>
-      <c r="D6" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="G6" t="n">
-        <v>362.25</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1108.49</v>
-      </c>
-      <c r="I6" t="n">
-        <v>697.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>697.9</v>
+          <t>7901064725409</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>939.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>46.95</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>985.95</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3017.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1960.90</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1960.90</t>
+        </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>19/08/2055</t>
+          <t>04/03/2056</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -6616,38 +6339,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7901064702752</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>229</v>
-      </c>
-      <c r="C7" t="n">
-        <v>345</v>
-      </c>
-      <c r="D7" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="G7" t="n">
-        <v>362.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1108.49</v>
-      </c>
-      <c r="I7" t="n">
-        <v>697.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>697.9</v>
+          <t>7901064725416</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>939.00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>46.95</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>985.95</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3017.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1960.90</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1960.90</t>
+        </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>19/08/2055</t>
+          <t>04/03/2056</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -6659,38 +6401,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7901064702769</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>229</v>
-      </c>
-      <c r="C8" t="n">
-        <v>345</v>
-      </c>
-      <c r="D8" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="G8" t="n">
-        <v>362.25</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1108.49</v>
-      </c>
-      <c r="I8" t="n">
-        <v>697.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>697.9</v>
+          <t>7901064725423</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1509.00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>75.45</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1584.45</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4848.41</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3150.90</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>3150.90</t>
+        </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>19/08/2055</t>
+          <t>04/03/2056</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -6702,38 +6463,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7901064702776</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>229</v>
-      </c>
-      <c r="C9" t="n">
-        <v>345</v>
-      </c>
-      <c r="D9" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="G9" t="n">
-        <v>362.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1108.49</v>
-      </c>
-      <c r="I9" t="n">
-        <v>697.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>697.9</v>
+          <t>7901064725430</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1509.00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>75.45</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1584.45</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4848.41</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3150.90</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3150.90</t>
+        </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>19/08/2055</t>
+          <t>04/03/2056</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -6745,256 +6525,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7901064702783</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>229</v>
-      </c>
-      <c r="C10" t="n">
-        <v>375</v>
-      </c>
-      <c r="D10" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="G10" t="n">
-        <v>393.75</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1204.88</v>
-      </c>
-      <c r="I10" t="n">
-        <v>758.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>758.9</v>
+          <t>7901064725447</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>105.00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>110.25</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>337.36</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>218.90</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>218.90</t>
+        </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>19/08/2055</t>
+          <t>04/03/2056</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>7901064702790</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>229</v>
-      </c>
-      <c r="C11" t="n">
-        <v>375</v>
-      </c>
-      <c r="D11" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="G11" t="n">
-        <v>393.75</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1204.88</v>
-      </c>
-      <c r="I11" t="n">
-        <v>758.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>758.9</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>19/08/2025</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>19/08/2055</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>7901064702806</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>229</v>
-      </c>
-      <c r="C12" t="n">
-        <v>375</v>
-      </c>
-      <c r="D12" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="G12" t="n">
-        <v>393.75</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1204.88</v>
-      </c>
-      <c r="I12" t="n">
-        <v>758.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>758.9</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>19/08/2025</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>19/08/2055</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>7901064702813</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>229</v>
-      </c>
-      <c r="C13" t="n">
-        <v>375</v>
-      </c>
-      <c r="D13" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="G13" t="n">
-        <v>393.75</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1204.88</v>
-      </c>
-      <c r="I13" t="n">
-        <v>758.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>758.9</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>19/08/2025</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>19/08/2055</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>7901064702820</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>229</v>
-      </c>
-      <c r="C14" t="n">
-        <v>260</v>
-      </c>
-      <c r="D14" t="n">
-        <v>13</v>
-      </c>
-      <c r="G14" t="n">
-        <v>273</v>
-      </c>
-      <c r="H14" t="n">
-        <v>835.38</v>
-      </c>
-      <c r="I14" t="n">
-        <v>525.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>525.9</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>19/08/2025</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>19/08/2055</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>7901064702837</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>229</v>
-      </c>
-      <c r="C15" t="n">
-        <v>260</v>
-      </c>
-      <c r="D15" t="n">
-        <v>13</v>
-      </c>
-      <c r="G15" t="n">
-        <v>273</v>
-      </c>
-      <c r="H15" t="n">
-        <v>835.38</v>
-      </c>
-      <c r="I15" t="n">
-        <v>525.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>525.9</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>19/08/2025</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>19/08/2055</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -7013,7 +6597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="23.28515625" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -7137,11 +6721,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7901064702707</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>398</v>
+          <t>7901064725362</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -7150,14 +6736,18 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>122</v>
-      </c>
-      <c r="O2" t="n">
-        <v>171</v>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -7173,11 +6763,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7901064702714</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>398</v>
+          <t>7901064725379</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -7186,14 +6778,18 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>122</v>
-      </c>
-      <c r="O3" t="n">
-        <v>171</v>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -7209,11 +6805,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7901064702721</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>338</v>
+          <t>7901064725386</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -7222,14 +6820,18 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>124</v>
-      </c>
-      <c r="O4" t="n">
-        <v>171</v>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -7245,11 +6847,13 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7901064702738</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>338</v>
+          <t>7901064725393</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -7258,14 +6862,18 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>124</v>
-      </c>
-      <c r="O5" t="n">
-        <v>171</v>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -7281,11 +6889,13 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7901064702745</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>338</v>
+          <t>7901064725409</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -7294,14 +6904,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>124</v>
-      </c>
-      <c r="O6" t="n">
-        <v>171</v>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -7317,11 +6931,13 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7901064702752</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>338</v>
+          <t>7901064725416</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -7330,14 +6946,18 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>124</v>
-      </c>
-      <c r="O7" t="n">
-        <v>171</v>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -7353,11 +6973,13 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7901064702769</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>338</v>
+          <t>7901064725423</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -7366,14 +6988,18 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>124</v>
-      </c>
-      <c r="O8" t="n">
-        <v>171</v>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -7389,11 +7015,13 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7901064702776</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>338</v>
+          <t>7901064725430</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -7402,14 +7030,18 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>124</v>
-      </c>
-      <c r="O9" t="n">
-        <v>171</v>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -7425,11 +7057,13 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7901064702783</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>338</v>
+          <t>7901064725447</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -7438,14 +7072,18 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>124</v>
-      </c>
-      <c r="O10" t="n">
-        <v>171</v>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -7453,186 +7091,6 @@
         </is>
       </c>
       <c r="S10" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>7901064702790</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>338</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>124</v>
-      </c>
-      <c r="O11" t="n">
-        <v>171</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>7901064702806</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>338</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>124</v>
-      </c>
-      <c r="O12" t="n">
-        <v>171</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>7901064702813</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>338</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>124</v>
-      </c>
-      <c r="O13" t="n">
-        <v>171</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>7901064702820</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>331</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>70</v>
-      </c>
-      <c r="O14" t="n">
-        <v>171</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>7901064702837</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>331</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>70</v>
-      </c>
-      <c r="O15" t="n">
-        <v>171</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -7650,7 +7108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col width="42.140625" bestFit="1" customWidth="1" style="12" min="1" max="1"/>
@@ -7693,276 +7151,6 @@
       <c r="F1" s="11" t="inlineStr">
         <is>
           <t>% DESC VENDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>7901064702738</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7901064702721</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>GR 4 PT IDEAL/MAYRA NT/CHP/BRISA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>7901064702738</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>7908816372904</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Desconhecido</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>7901064702783</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>7901064702745</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>GR 6 PT IDEAL/MAYRA BRANCO FLEX</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>7901064702783</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7908816372904</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Desconhecido</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>7901064702790</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>7901064702752</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>GR 6 PT IDEAL/MAYRA IMBUIA/CHP</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7901064702790</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>7908816372904</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Desconhecido</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7901064702806</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>7901064702769</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GR 6 PT IDEAL/MAYRA IMBUIA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7901064702806</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>7908816372904</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Desconhecido</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>7901064702813</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>7901064702776</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>GR 6 PT IDEAL/MAYRA NT/CHP/BRISA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>7901064702813</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>7908816372904</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Desconhecido</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -8061,28 +7249,38 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>7901064702707</t>
+          <t>7901064725362</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MULTIUSO LINE/ALINE IMBUIA/CHP</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>37</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36</v>
-      </c>
-      <c r="E2" t="n">
-        <v>61</v>
-      </c>
-      <c r="F2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H2" t="n">
-        <v>190</v>
+          <t>COMODA DUBAI INT/DELMONT NATURE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>19,5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>50,5</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -8101,28 +7299,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7901064702714</t>
+          <t>7901064725362</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MULTIUSO LINE/ALINE IMBUIA</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>37</v>
-      </c>
-      <c r="D3" t="n">
-        <v>36</v>
-      </c>
-      <c r="E3" t="n">
-        <v>61</v>
-      </c>
-      <c r="F3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H3" t="n">
-        <v>190</v>
+          <t>COMODA DUBAI INT/DELMONT NATURE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>19,5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>50,5</t>
+        </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -8135,34 +7343,44 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7901064702721</t>
+          <t>7901064725379</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GR 4 PT IDEAL/MAYRA NT/CHP/BRISA</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>44</v>
-      </c>
-      <c r="D4" t="n">
-        <v>43</v>
-      </c>
-      <c r="E4" t="n">
-        <v>51</v>
-      </c>
-      <c r="F4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H4" t="n">
-        <v>180</v>
+          <t>COMODA DUBAI INT/DELMONT NATURE/ALASCA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>19,5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>50,5</t>
+        </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -8181,28 +7399,38 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7901064702738</t>
+          <t>7901064725379</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GR 4 PT C/ESP IDEAL/MAYRA NT/CHP/BRISA</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15.66666667</v>
-      </c>
-      <c r="D5" t="n">
-        <v>15.33333333</v>
-      </c>
-      <c r="E5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" t="n">
-        <v>9.666666666999999</v>
-      </c>
-      <c r="H5" t="n">
-        <v>33.66666667</v>
+          <t>COMODA DUBAI INT/DELMONT NATURE/ALASCA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>19,5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>50,5</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -8215,34 +7443,44 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7901064702738</t>
+          <t>7901064725386</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GR 4 PT C/ESP IDEAL/MAYRA NT/CHP/BRISA</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>15.66666667</v>
-      </c>
-      <c r="D6" t="n">
-        <v>15.33333333</v>
-      </c>
-      <c r="E6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" t="n">
-        <v>9.666666666999999</v>
-      </c>
-      <c r="H6" t="n">
-        <v>33.66666667</v>
+          <t>COMODA DUBAI INT/DELMONT NATURE/CAMARIM</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>19,5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>50,5</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -8255,34 +7493,44 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7901064702738</t>
+          <t>7901064725386</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GR 4 PT C/ESP IDEAL/MAYRA NT/CHP/BRISA</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>15.66666667</v>
-      </c>
-      <c r="D7" t="n">
-        <v>15.33333333</v>
-      </c>
-      <c r="E7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" t="n">
-        <v>9.666666666999999</v>
-      </c>
-      <c r="H7" t="n">
-        <v>33.66666667</v>
+          <t>COMODA DUBAI INT/DELMONT NATURE/CAMARIM</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>19,5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>50,5</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -8295,34 +7543,44 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7901064702745</t>
+          <t>7901064725393</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA BRANCO FLEX</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>61</v>
-      </c>
-      <c r="D8" t="n">
-        <v>60</v>
-      </c>
-      <c r="E8" t="n">
-        <v>51</v>
-      </c>
-      <c r="F8" t="n">
-        <v>12</v>
-      </c>
-      <c r="H8" t="n">
-        <v>180</v>
+          <t>COMODA DUBAI INT/DELMONT NATURE/FENDI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>19,5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>50,5</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -8341,28 +7599,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7901064702752</t>
+          <t>7901064725393</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA IMBUIA/CHP</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>61</v>
-      </c>
-      <c r="D9" t="n">
-        <v>60</v>
-      </c>
-      <c r="E9" t="n">
-        <v>51</v>
-      </c>
-      <c r="F9" t="n">
-        <v>12</v>
-      </c>
-      <c r="H9" t="n">
-        <v>180</v>
+          <t>COMODA DUBAI INT/DELMONT NATURE/FENDI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>19,5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>50,5</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -8375,34 +7643,44 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7901064702769</t>
+          <t>7901064725409</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA IMBUIA</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>61</v>
-      </c>
-      <c r="D10" t="n">
-        <v>60</v>
-      </c>
-      <c r="E10" t="n">
-        <v>51</v>
-      </c>
-      <c r="F10" t="n">
-        <v>12</v>
-      </c>
-      <c r="H10" t="n">
-        <v>180</v>
+          <t>GUARDA ROUPA DUBAI INF/ZANE NATURE/FENDI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>43,66666667</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>16,33333333</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>33,66666667</t>
+        </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -8421,28 +7699,38 @@
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>7901064702776</t>
+          <t>7901064725409</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GR 6 PT IDEAL/MAYRA NT/CHP/BRISA</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>61</v>
-      </c>
-      <c r="D11" t="n">
-        <v>60</v>
-      </c>
-      <c r="E11" t="n">
-        <v>51</v>
-      </c>
-      <c r="F11" t="n">
-        <v>12</v>
-      </c>
-      <c r="H11" t="n">
-        <v>180</v>
+          <t>GUARDA ROUPA DUBAI INF/ZANE NATURE/FENDI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>43,66666667</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>16,33333333</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>33,66666667</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -8455,34 +7743,44 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7901064702783</t>
+          <t>7901064725409</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA BRANCO</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>21.33333333</v>
-      </c>
-      <c r="D12" t="n">
-        <v>21</v>
-      </c>
-      <c r="E12" t="n">
-        <v>11.66666667</v>
-      </c>
-      <c r="F12" t="n">
-        <v>11.33333333</v>
-      </c>
-      <c r="H12" t="n">
-        <v>33.66666667</v>
+          <t>GUARDA ROUPA DUBAI INF/ZANE NATURE/FENDI</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>43,66666667</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>16,33333333</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>33,66666667</t>
+        </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -8495,34 +7793,44 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7901064702783</t>
+          <t>7901064725416</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA BRANCO</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>21.33333333</v>
-      </c>
-      <c r="D13" t="n">
-        <v>21</v>
-      </c>
-      <c r="E13" t="n">
-        <v>11.66666667</v>
-      </c>
-      <c r="F13" t="n">
-        <v>11.33333333</v>
-      </c>
-      <c r="H13" t="n">
-        <v>33.66666667</v>
+          <t>GUARDA ROUPA DUBAI INF/ZANE NT/CRM/ALS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>43,66666667</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>16,33333333</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>33,66666667</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -8535,34 +7843,44 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7901064702783</t>
+          <t>7901064725416</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA BRANCO</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>21.33333333</v>
-      </c>
-      <c r="D14" t="n">
-        <v>21</v>
-      </c>
-      <c r="E14" t="n">
-        <v>11.66666667</v>
-      </c>
-      <c r="F14" t="n">
-        <v>11.33333333</v>
-      </c>
-      <c r="H14" t="n">
-        <v>33.66666667</v>
+          <t>GUARDA ROUPA DUBAI INF/ZANE NT/CRM/ALS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>43,66666667</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>16,33333333</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>33,66666667</t>
+        </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -8575,34 +7893,44 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7901064702790</t>
+          <t>7901064725416</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA IMBUIA/CHP</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>21.33333333</v>
-      </c>
-      <c r="D15" t="n">
-        <v>21</v>
-      </c>
-      <c r="E15" t="n">
-        <v>11.66666667</v>
-      </c>
-      <c r="F15" t="n">
-        <v>11.33333333</v>
-      </c>
-      <c r="H15" t="n">
-        <v>33.66666667</v>
+          <t>GUARDA ROUPA DUBAI INF/ZANE NT/CRM/ALS</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>43,66666667</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>16,33333333</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>33,66666667</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -8615,34 +7943,44 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7901064702790</t>
+          <t>7901064725423</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA IMBUIA/CHP</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>21.33333333</v>
-      </c>
-      <c r="D16" t="n">
-        <v>21</v>
-      </c>
-      <c r="E16" t="n">
-        <v>11.66666667</v>
-      </c>
-      <c r="F16" t="n">
-        <v>11.33333333</v>
-      </c>
-      <c r="H16" t="n">
-        <v>33.66666667</v>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/ALS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>33,5</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>33,33333333</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>31,33333333</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>16,83333333</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -8655,34 +7993,44 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7901064702790</t>
+          <t>7901064725423</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA IMBUIA/CHP</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>21.33333333</v>
-      </c>
-      <c r="D17" t="n">
-        <v>21</v>
-      </c>
-      <c r="E17" t="n">
-        <v>11.66666667</v>
-      </c>
-      <c r="F17" t="n">
-        <v>11.33333333</v>
-      </c>
-      <c r="H17" t="n">
-        <v>33.66666667</v>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/ALS</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>33,5</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>33,33333333</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>31,33333333</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>16,83333333</t>
+        </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -8695,34 +8043,44 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7901064702806</t>
+          <t>7901064725423</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA IMBUIA</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>21.33333333</v>
-      </c>
-      <c r="D18" t="n">
-        <v>21</v>
-      </c>
-      <c r="E18" t="n">
-        <v>11.66666667</v>
-      </c>
-      <c r="F18" t="n">
-        <v>11.33333333</v>
-      </c>
-      <c r="H18" t="n">
-        <v>33.66666667</v>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/ALS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>33,5</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>33,33333333</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>31,33333333</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>16,83333333</t>
+        </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -8735,34 +8093,44 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7901064702806</t>
+          <t>7901064725423</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA IMBUIA</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>21.33333333</v>
-      </c>
-      <c r="D19" t="n">
-        <v>21</v>
-      </c>
-      <c r="E19" t="n">
-        <v>11.66666667</v>
-      </c>
-      <c r="F19" t="n">
-        <v>11.33333333</v>
-      </c>
-      <c r="H19" t="n">
-        <v>33.66666667</v>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/ALS</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>33,5</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>33,33333333</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>31,33333333</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>16,83333333</t>
+        </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -8775,34 +8143,44 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7901064702806</t>
+          <t>7901064725423</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA IMBUIA</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>21.33333333</v>
-      </c>
-      <c r="D20" t="n">
-        <v>21</v>
-      </c>
-      <c r="E20" t="n">
-        <v>11.66666667</v>
-      </c>
-      <c r="F20" t="n">
-        <v>11.33333333</v>
-      </c>
-      <c r="H20" t="n">
-        <v>33.66666667</v>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/ALS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>33,5</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>33,33333333</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>31,33333333</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>16,83333333</t>
+        </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -8815,34 +8193,44 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>7901064702813</t>
+          <t>7901064725423</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA NT/CHP/BRISA</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>21.33333333</v>
-      </c>
-      <c r="D21" t="n">
-        <v>21</v>
-      </c>
-      <c r="E21" t="n">
-        <v>11.66666667</v>
-      </c>
-      <c r="F21" t="n">
-        <v>11.33333333</v>
-      </c>
-      <c r="H21" t="n">
-        <v>33.66666667</v>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/ALS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>33,5</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>33,33333333</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>31,33333333</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>16,83333333</t>
+        </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -8855,34 +8243,44 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7901064702813</t>
+          <t>7901064725430</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA NT/CHP/BRISA</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>21.33333333</v>
-      </c>
-      <c r="D22" t="n">
-        <v>21</v>
-      </c>
-      <c r="E22" t="n">
-        <v>11.66666667</v>
-      </c>
-      <c r="F22" t="n">
-        <v>11.33333333</v>
-      </c>
-      <c r="H22" t="n">
-        <v>33.66666667</v>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/FEN</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>33,5</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>33,33333333</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>31,33333333</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>16,83333333</t>
+        </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -8895,34 +8293,44 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7901064702813</t>
+          <t>7901064725430</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GR 6 PT C/ESP IDEAL/MAYRA NT/CHP/BRISA</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>21.33333333</v>
-      </c>
-      <c r="D23" t="n">
-        <v>21</v>
-      </c>
-      <c r="E23" t="n">
-        <v>11.66666667</v>
-      </c>
-      <c r="F23" t="n">
-        <v>11.33333333</v>
-      </c>
-      <c r="H23" t="n">
-        <v>33.66666667</v>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/FEN</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>33,5</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>33,33333333</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>31,33333333</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>16,83333333</t>
+        </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -8935,34 +8343,44 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7901064702820</t>
+          <t>7901064725430</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>COMODA SIRIUS/LIRIO IMBUIA/CHP</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>44</v>
-      </c>
-      <c r="D24" t="n">
-        <v>43</v>
-      </c>
-      <c r="E24" t="n">
-        <v>48</v>
-      </c>
-      <c r="F24" t="n">
-        <v>16</v>
-      </c>
-      <c r="H24" t="n">
-        <v>129</v>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/FEN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>33,5</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>33,33333333</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>31,33333333</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>16,83333333</t>
+        </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -8975,34 +8393,44 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7901064702837</t>
+          <t>7901064725430</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>COMODA SIRIUS/LIRIO IMBUIA</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>44</v>
-      </c>
-      <c r="D25" t="n">
-        <v>43</v>
-      </c>
-      <c r="E25" t="n">
-        <v>48</v>
-      </c>
-      <c r="F25" t="n">
-        <v>16</v>
-      </c>
-      <c r="H25" t="n">
-        <v>129</v>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/FEN</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>33,5</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>33,33333333</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>31,33333333</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>16,83333333</t>
+        </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -9015,6 +8443,156 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7901064725430</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/FEN</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>33,5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>33,33333333</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>31,33333333</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>16,83333333</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>BOX</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7901064725430</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GUARDA ROUPA DUBAI OUR/VONN REFLE NT/FEN</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>33,5</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>33,33333333</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>31,5</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>31,33333333</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>16,83333333</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>BOX</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>7901064725447</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MESA DE CABECEIRA DUBAI/LIOR NATURE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>BOX</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
     </row>
